--- a/portal/templates/01 Xero P&L.xlsx
+++ b/portal/templates/01 Xero P&L.xlsx
@@ -11,7 +11,7 @@
     <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P&amp;L'!$A$1:$Y$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P&amp;L'!$A$1:$AK$262</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -592,29 +592,50 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>At the start of a financial year</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to set up. The columns run three years across, and the portal reads the month from each heading, so July's paste goes in July's column and the new year appears on its own. Keep the prior year's columns filled: revenue shares and same month last year come off them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>When the last year across is the one you are in, add the next twelve months to the right of the last column, headed the same way (Jul-28, Aug-28 and so on), on this tab and on the Budget tab of 07 Budget. Columns older than two years back can be deleted once the archive folder holds them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Cream cells with blue text: paste or type here.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Yellow cells: a setting you choose.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Grey cells: calculated or fixed. Do not type here.</t>
         </is>
@@ -631,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA262"/>
+  <dimension ref="A1:AM262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -659,6 +680,18 @@
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -787,9 +820,69 @@
           <t>Jun-27</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>FY26 in columns B to M, FY27 in N to Y. Income positive, costs positive as Xero shows them.</t>
+      <c r="Z1" s="8" t="inlineStr">
+        <is>
+          <t>Jul-27</t>
+        </is>
+      </c>
+      <c r="AA1" s="8" t="inlineStr">
+        <is>
+          <t>Aug-27</t>
+        </is>
+      </c>
+      <c r="AB1" s="8" t="inlineStr">
+        <is>
+          <t>Sep-27</t>
+        </is>
+      </c>
+      <c r="AC1" s="8" t="inlineStr">
+        <is>
+          <t>Oct-27</t>
+        </is>
+      </c>
+      <c r="AD1" s="8" t="inlineStr">
+        <is>
+          <t>Nov-27</t>
+        </is>
+      </c>
+      <c r="AE1" s="8" t="inlineStr">
+        <is>
+          <t>Dec-27</t>
+        </is>
+      </c>
+      <c r="AF1" s="8" t="inlineStr">
+        <is>
+          <t>Jan-28</t>
+        </is>
+      </c>
+      <c r="AG1" s="8" t="inlineStr">
+        <is>
+          <t>Feb-28</t>
+        </is>
+      </c>
+      <c r="AH1" s="8" t="inlineStr">
+        <is>
+          <t>Mar-28</t>
+        </is>
+      </c>
+      <c r="AI1" s="8" t="inlineStr">
+        <is>
+          <t>Apr-28</t>
+        </is>
+      </c>
+      <c r="AJ1" s="8" t="inlineStr">
+        <is>
+          <t>May-28</t>
+        </is>
+      </c>
+      <c r="AK1" s="8" t="inlineStr">
+        <is>
+          <t>Jun-28</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>FY26 in columns B to M, FY27 in N to Y, FY28 in Z to AK. Income positive, costs positive as Xero shows them. Add columns to the right for later years.</t>
         </is>
       </c>
     </row>
@@ -869,6 +962,42 @@
         <v>0</v>
       </c>
       <c r="Y2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -902,6 +1031,18 @@
       <c r="W3" s="11" t="n"/>
       <c r="X3" s="11" t="n"/>
       <c r="Y3" s="11" t="n"/>
+      <c r="Z3" s="11" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="11" t="n"/>
+      <c r="AD3" s="11" t="n"/>
+      <c r="AE3" s="11" t="n"/>
+      <c r="AF3" s="11" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+      <c r="AI3" s="11" t="n"/>
+      <c r="AJ3" s="11" t="n"/>
+      <c r="AK3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -933,6 +1074,18 @@
       <c r="W4" s="11" t="n"/>
       <c r="X4" s="11" t="n"/>
       <c r="Y4" s="11" t="n"/>
+      <c r="Z4" s="11" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="11" t="n"/>
+      <c r="AD4" s="11" t="n"/>
+      <c r="AE4" s="11" t="n"/>
+      <c r="AF4" s="11" t="n"/>
+      <c r="AG4" s="11" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+      <c r="AI4" s="11" t="n"/>
+      <c r="AJ4" s="11" t="n"/>
+      <c r="AK4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -964,6 +1117,18 @@
       <c r="W5" s="11" t="n"/>
       <c r="X5" s="11" t="n"/>
       <c r="Y5" s="11" t="n"/>
+      <c r="Z5" s="11" t="n"/>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="11" t="n"/>
+      <c r="AC5" s="11" t="n"/>
+      <c r="AD5" s="11" t="n"/>
+      <c r="AE5" s="11" t="n"/>
+      <c r="AF5" s="11" t="n"/>
+      <c r="AG5" s="11" t="n"/>
+      <c r="AH5" s="11" t="n"/>
+      <c r="AI5" s="11" t="n"/>
+      <c r="AJ5" s="11" t="n"/>
+      <c r="AK5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -995,6 +1160,18 @@
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="11" t="n"/>
       <c r="Y6" s="11" t="n"/>
+      <c r="Z6" s="11" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="11" t="n"/>
+      <c r="AC6" s="11" t="n"/>
+      <c r="AD6" s="11" t="n"/>
+      <c r="AE6" s="11" t="n"/>
+      <c r="AF6" s="11" t="n"/>
+      <c r="AG6" s="11" t="n"/>
+      <c r="AH6" s="11" t="n"/>
+      <c r="AI6" s="11" t="n"/>
+      <c r="AJ6" s="11" t="n"/>
+      <c r="AK6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1026,6 +1203,18 @@
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="11" t="n"/>
       <c r="Y7" s="11" t="n"/>
+      <c r="Z7" s="11" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="11" t="n"/>
+      <c r="AC7" s="11" t="n"/>
+      <c r="AD7" s="11" t="n"/>
+      <c r="AE7" s="11" t="n"/>
+      <c r="AF7" s="11" t="n"/>
+      <c r="AG7" s="11" t="n"/>
+      <c r="AH7" s="11" t="n"/>
+      <c r="AI7" s="11" t="n"/>
+      <c r="AJ7" s="11" t="n"/>
+      <c r="AK7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1057,6 +1246,18 @@
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="11" t="n"/>
       <c r="Y8" s="11" t="n"/>
+      <c r="Z8" s="11" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="11" t="n"/>
+      <c r="AC8" s="11" t="n"/>
+      <c r="AD8" s="11" t="n"/>
+      <c r="AE8" s="11" t="n"/>
+      <c r="AF8" s="11" t="n"/>
+      <c r="AG8" s="11" t="n"/>
+      <c r="AH8" s="11" t="n"/>
+      <c r="AI8" s="11" t="n"/>
+      <c r="AJ8" s="11" t="n"/>
+      <c r="AK8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1088,6 +1289,18 @@
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="11" t="n"/>
       <c r="Y9" s="11" t="n"/>
+      <c r="Z9" s="11" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="11" t="n"/>
+      <c r="AC9" s="11" t="n"/>
+      <c r="AD9" s="11" t="n"/>
+      <c r="AE9" s="11" t="n"/>
+      <c r="AF9" s="11" t="n"/>
+      <c r="AG9" s="11" t="n"/>
+      <c r="AH9" s="11" t="n"/>
+      <c r="AI9" s="11" t="n"/>
+      <c r="AJ9" s="11" t="n"/>
+      <c r="AK9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1119,6 +1332,18 @@
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="11" t="n"/>
       <c r="Y10" s="11" t="n"/>
+      <c r="Z10" s="11" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="11" t="n"/>
+      <c r="AC10" s="11" t="n"/>
+      <c r="AD10" s="11" t="n"/>
+      <c r="AE10" s="11" t="n"/>
+      <c r="AF10" s="11" t="n"/>
+      <c r="AG10" s="11" t="n"/>
+      <c r="AH10" s="11" t="n"/>
+      <c r="AI10" s="11" t="n"/>
+      <c r="AJ10" s="11" t="n"/>
+      <c r="AK10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1150,6 +1375,18 @@
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="11" t="n"/>
       <c r="Y11" s="11" t="n"/>
+      <c r="Z11" s="11" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="11" t="n"/>
+      <c r="AC11" s="11" t="n"/>
+      <c r="AD11" s="11" t="n"/>
+      <c r="AE11" s="11" t="n"/>
+      <c r="AF11" s="11" t="n"/>
+      <c r="AG11" s="11" t="n"/>
+      <c r="AH11" s="11" t="n"/>
+      <c r="AI11" s="11" t="n"/>
+      <c r="AJ11" s="11" t="n"/>
+      <c r="AK11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1181,6 +1418,18 @@
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="11" t="n"/>
       <c r="Y12" s="11" t="n"/>
+      <c r="Z12" s="11" t="n"/>
+      <c r="AA12" s="11" t="n"/>
+      <c r="AB12" s="11" t="n"/>
+      <c r="AC12" s="11" t="n"/>
+      <c r="AD12" s="11" t="n"/>
+      <c r="AE12" s="11" t="n"/>
+      <c r="AF12" s="11" t="n"/>
+      <c r="AG12" s="11" t="n"/>
+      <c r="AH12" s="11" t="n"/>
+      <c r="AI12" s="11" t="n"/>
+      <c r="AJ12" s="11" t="n"/>
+      <c r="AK12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1212,6 +1461,18 @@
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="11" t="n"/>
       <c r="Y13" s="11" t="n"/>
+      <c r="Z13" s="11" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="11" t="n"/>
+      <c r="AC13" s="11" t="n"/>
+      <c r="AD13" s="11" t="n"/>
+      <c r="AE13" s="11" t="n"/>
+      <c r="AF13" s="11" t="n"/>
+      <c r="AG13" s="11" t="n"/>
+      <c r="AH13" s="11" t="n"/>
+      <c r="AI13" s="11" t="n"/>
+      <c r="AJ13" s="11" t="n"/>
+      <c r="AK13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1243,6 +1504,18 @@
       <c r="W14" s="11" t="n"/>
       <c r="X14" s="11" t="n"/>
       <c r="Y14" s="11" t="n"/>
+      <c r="Z14" s="11" t="n"/>
+      <c r="AA14" s="11" t="n"/>
+      <c r="AB14" s="11" t="n"/>
+      <c r="AC14" s="11" t="n"/>
+      <c r="AD14" s="11" t="n"/>
+      <c r="AE14" s="11" t="n"/>
+      <c r="AF14" s="11" t="n"/>
+      <c r="AG14" s="11" t="n"/>
+      <c r="AH14" s="11" t="n"/>
+      <c r="AI14" s="11" t="n"/>
+      <c r="AJ14" s="11" t="n"/>
+      <c r="AK14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1274,6 +1547,18 @@
       <c r="W15" s="11" t="n"/>
       <c r="X15" s="11" t="n"/>
       <c r="Y15" s="11" t="n"/>
+      <c r="Z15" s="11" t="n"/>
+      <c r="AA15" s="11" t="n"/>
+      <c r="AB15" s="11" t="n"/>
+      <c r="AC15" s="11" t="n"/>
+      <c r="AD15" s="11" t="n"/>
+      <c r="AE15" s="11" t="n"/>
+      <c r="AF15" s="11" t="n"/>
+      <c r="AG15" s="11" t="n"/>
+      <c r="AH15" s="11" t="n"/>
+      <c r="AI15" s="11" t="n"/>
+      <c r="AJ15" s="11" t="n"/>
+      <c r="AK15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1305,6 +1590,18 @@
       <c r="W16" s="11" t="n"/>
       <c r="X16" s="11" t="n"/>
       <c r="Y16" s="11" t="n"/>
+      <c r="Z16" s="11" t="n"/>
+      <c r="AA16" s="11" t="n"/>
+      <c r="AB16" s="11" t="n"/>
+      <c r="AC16" s="11" t="n"/>
+      <c r="AD16" s="11" t="n"/>
+      <c r="AE16" s="11" t="n"/>
+      <c r="AF16" s="11" t="n"/>
+      <c r="AG16" s="11" t="n"/>
+      <c r="AH16" s="11" t="n"/>
+      <c r="AI16" s="11" t="n"/>
+      <c r="AJ16" s="11" t="n"/>
+      <c r="AK16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1336,6 +1633,18 @@
       <c r="W17" s="11" t="n"/>
       <c r="X17" s="11" t="n"/>
       <c r="Y17" s="11" t="n"/>
+      <c r="Z17" s="11" t="n"/>
+      <c r="AA17" s="11" t="n"/>
+      <c r="AB17" s="11" t="n"/>
+      <c r="AC17" s="11" t="n"/>
+      <c r="AD17" s="11" t="n"/>
+      <c r="AE17" s="11" t="n"/>
+      <c r="AF17" s="11" t="n"/>
+      <c r="AG17" s="11" t="n"/>
+      <c r="AH17" s="11" t="n"/>
+      <c r="AI17" s="11" t="n"/>
+      <c r="AJ17" s="11" t="n"/>
+      <c r="AK17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1367,6 +1676,18 @@
       <c r="W18" s="11" t="n"/>
       <c r="X18" s="11" t="n"/>
       <c r="Y18" s="11" t="n"/>
+      <c r="Z18" s="11" t="n"/>
+      <c r="AA18" s="11" t="n"/>
+      <c r="AB18" s="11" t="n"/>
+      <c r="AC18" s="11" t="n"/>
+      <c r="AD18" s="11" t="n"/>
+      <c r="AE18" s="11" t="n"/>
+      <c r="AF18" s="11" t="n"/>
+      <c r="AG18" s="11" t="n"/>
+      <c r="AH18" s="11" t="n"/>
+      <c r="AI18" s="11" t="n"/>
+      <c r="AJ18" s="11" t="n"/>
+      <c r="AK18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1398,6 +1719,18 @@
       <c r="W19" s="11" t="n"/>
       <c r="X19" s="11" t="n"/>
       <c r="Y19" s="11" t="n"/>
+      <c r="Z19" s="11" t="n"/>
+      <c r="AA19" s="11" t="n"/>
+      <c r="AB19" s="11" t="n"/>
+      <c r="AC19" s="11" t="n"/>
+      <c r="AD19" s="11" t="n"/>
+      <c r="AE19" s="11" t="n"/>
+      <c r="AF19" s="11" t="n"/>
+      <c r="AG19" s="11" t="n"/>
+      <c r="AH19" s="11" t="n"/>
+      <c r="AI19" s="11" t="n"/>
+      <c r="AJ19" s="11" t="n"/>
+      <c r="AK19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1429,6 +1762,18 @@
       <c r="W20" s="11" t="n"/>
       <c r="X20" s="11" t="n"/>
       <c r="Y20" s="11" t="n"/>
+      <c r="Z20" s="11" t="n"/>
+      <c r="AA20" s="11" t="n"/>
+      <c r="AB20" s="11" t="n"/>
+      <c r="AC20" s="11" t="n"/>
+      <c r="AD20" s="11" t="n"/>
+      <c r="AE20" s="11" t="n"/>
+      <c r="AF20" s="11" t="n"/>
+      <c r="AG20" s="11" t="n"/>
+      <c r="AH20" s="11" t="n"/>
+      <c r="AI20" s="11" t="n"/>
+      <c r="AJ20" s="11" t="n"/>
+      <c r="AK20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1460,6 +1805,18 @@
       <c r="W21" s="11" t="n"/>
       <c r="X21" s="11" t="n"/>
       <c r="Y21" s="11" t="n"/>
+      <c r="Z21" s="11" t="n"/>
+      <c r="AA21" s="11" t="n"/>
+      <c r="AB21" s="11" t="n"/>
+      <c r="AC21" s="11" t="n"/>
+      <c r="AD21" s="11" t="n"/>
+      <c r="AE21" s="11" t="n"/>
+      <c r="AF21" s="11" t="n"/>
+      <c r="AG21" s="11" t="n"/>
+      <c r="AH21" s="11" t="n"/>
+      <c r="AI21" s="11" t="n"/>
+      <c r="AJ21" s="11" t="n"/>
+      <c r="AK21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1491,6 +1848,18 @@
       <c r="W22" s="11" t="n"/>
       <c r="X22" s="11" t="n"/>
       <c r="Y22" s="11" t="n"/>
+      <c r="Z22" s="11" t="n"/>
+      <c r="AA22" s="11" t="n"/>
+      <c r="AB22" s="11" t="n"/>
+      <c r="AC22" s="11" t="n"/>
+      <c r="AD22" s="11" t="n"/>
+      <c r="AE22" s="11" t="n"/>
+      <c r="AF22" s="11" t="n"/>
+      <c r="AG22" s="11" t="n"/>
+      <c r="AH22" s="11" t="n"/>
+      <c r="AI22" s="11" t="n"/>
+      <c r="AJ22" s="11" t="n"/>
+      <c r="AK22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1522,6 +1891,18 @@
       <c r="W23" s="11" t="n"/>
       <c r="X23" s="11" t="n"/>
       <c r="Y23" s="11" t="n"/>
+      <c r="Z23" s="11" t="n"/>
+      <c r="AA23" s="11" t="n"/>
+      <c r="AB23" s="11" t="n"/>
+      <c r="AC23" s="11" t="n"/>
+      <c r="AD23" s="11" t="n"/>
+      <c r="AE23" s="11" t="n"/>
+      <c r="AF23" s="11" t="n"/>
+      <c r="AG23" s="11" t="n"/>
+      <c r="AH23" s="11" t="n"/>
+      <c r="AI23" s="11" t="n"/>
+      <c r="AJ23" s="11" t="n"/>
+      <c r="AK23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1553,6 +1934,18 @@
       <c r="W24" s="11" t="n"/>
       <c r="X24" s="11" t="n"/>
       <c r="Y24" s="11" t="n"/>
+      <c r="Z24" s="11" t="n"/>
+      <c r="AA24" s="11" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="11" t="n"/>
+      <c r="AD24" s="11" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="11" t="n"/>
+      <c r="AG24" s="11" t="n"/>
+      <c r="AH24" s="11" t="n"/>
+      <c r="AI24" s="11" t="n"/>
+      <c r="AJ24" s="11" t="n"/>
+      <c r="AK24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1584,6 +1977,18 @@
       <c r="W25" s="11" t="n"/>
       <c r="X25" s="11" t="n"/>
       <c r="Y25" s="11" t="n"/>
+      <c r="Z25" s="11" t="n"/>
+      <c r="AA25" s="11" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="11" t="n"/>
+      <c r="AD25" s="11" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="11" t="n"/>
+      <c r="AG25" s="11" t="n"/>
+      <c r="AH25" s="11" t="n"/>
+      <c r="AI25" s="11" t="n"/>
+      <c r="AJ25" s="11" t="n"/>
+      <c r="AK25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1615,6 +2020,18 @@
       <c r="W26" s="11" t="n"/>
       <c r="X26" s="11" t="n"/>
       <c r="Y26" s="11" t="n"/>
+      <c r="Z26" s="11" t="n"/>
+      <c r="AA26" s="11" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="11" t="n"/>
+      <c r="AD26" s="11" t="n"/>
+      <c r="AE26" s="11" t="n"/>
+      <c r="AF26" s="11" t="n"/>
+      <c r="AG26" s="11" t="n"/>
+      <c r="AH26" s="11" t="n"/>
+      <c r="AI26" s="11" t="n"/>
+      <c r="AJ26" s="11" t="n"/>
+      <c r="AK26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1646,6 +2063,18 @@
       <c r="W27" s="11" t="n"/>
       <c r="X27" s="11" t="n"/>
       <c r="Y27" s="11" t="n"/>
+      <c r="Z27" s="11" t="n"/>
+      <c r="AA27" s="11" t="n"/>
+      <c r="AB27" s="11" t="n"/>
+      <c r="AC27" s="11" t="n"/>
+      <c r="AD27" s="11" t="n"/>
+      <c r="AE27" s="11" t="n"/>
+      <c r="AF27" s="11" t="n"/>
+      <c r="AG27" s="11" t="n"/>
+      <c r="AH27" s="11" t="n"/>
+      <c r="AI27" s="11" t="n"/>
+      <c r="AJ27" s="11" t="n"/>
+      <c r="AK27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1677,6 +2106,18 @@
       <c r="W28" s="11" t="n"/>
       <c r="X28" s="11" t="n"/>
       <c r="Y28" s="11" t="n"/>
+      <c r="Z28" s="11" t="n"/>
+      <c r="AA28" s="11" t="n"/>
+      <c r="AB28" s="11" t="n"/>
+      <c r="AC28" s="11" t="n"/>
+      <c r="AD28" s="11" t="n"/>
+      <c r="AE28" s="11" t="n"/>
+      <c r="AF28" s="11" t="n"/>
+      <c r="AG28" s="11" t="n"/>
+      <c r="AH28" s="11" t="n"/>
+      <c r="AI28" s="11" t="n"/>
+      <c r="AJ28" s="11" t="n"/>
+      <c r="AK28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1708,6 +2149,18 @@
       <c r="W29" s="11" t="n"/>
       <c r="X29" s="11" t="n"/>
       <c r="Y29" s="11" t="n"/>
+      <c r="Z29" s="11" t="n"/>
+      <c r="AA29" s="11" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="11" t="n"/>
+      <c r="AD29" s="11" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="11" t="n"/>
+      <c r="AG29" s="11" t="n"/>
+      <c r="AH29" s="11" t="n"/>
+      <c r="AI29" s="11" t="n"/>
+      <c r="AJ29" s="11" t="n"/>
+      <c r="AK29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1739,6 +2192,18 @@
       <c r="W30" s="11" t="n"/>
       <c r="X30" s="11" t="n"/>
       <c r="Y30" s="11" t="n"/>
+      <c r="Z30" s="11" t="n"/>
+      <c r="AA30" s="11" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="11" t="n"/>
+      <c r="AD30" s="11" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="11" t="n"/>
+      <c r="AG30" s="11" t="n"/>
+      <c r="AH30" s="11" t="n"/>
+      <c r="AI30" s="11" t="n"/>
+      <c r="AJ30" s="11" t="n"/>
+      <c r="AK30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1770,6 +2235,18 @@
       <c r="W31" s="11" t="n"/>
       <c r="X31" s="11" t="n"/>
       <c r="Y31" s="11" t="n"/>
+      <c r="Z31" s="11" t="n"/>
+      <c r="AA31" s="11" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="11" t="n"/>
+      <c r="AD31" s="11" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="11" t="n"/>
+      <c r="AG31" s="11" t="n"/>
+      <c r="AH31" s="11" t="n"/>
+      <c r="AI31" s="11" t="n"/>
+      <c r="AJ31" s="11" t="n"/>
+      <c r="AK31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1801,6 +2278,18 @@
       <c r="W32" s="11" t="n"/>
       <c r="X32" s="11" t="n"/>
       <c r="Y32" s="11" t="n"/>
+      <c r="Z32" s="11" t="n"/>
+      <c r="AA32" s="11" t="n"/>
+      <c r="AB32" s="11" t="n"/>
+      <c r="AC32" s="11" t="n"/>
+      <c r="AD32" s="11" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="11" t="n"/>
+      <c r="AG32" s="11" t="n"/>
+      <c r="AH32" s="11" t="n"/>
+      <c r="AI32" s="11" t="n"/>
+      <c r="AJ32" s="11" t="n"/>
+      <c r="AK32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1832,6 +2321,18 @@
       <c r="W33" s="11" t="n"/>
       <c r="X33" s="11" t="n"/>
       <c r="Y33" s="11" t="n"/>
+      <c r="Z33" s="11" t="n"/>
+      <c r="AA33" s="11" t="n"/>
+      <c r="AB33" s="11" t="n"/>
+      <c r="AC33" s="11" t="n"/>
+      <c r="AD33" s="11" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="11" t="n"/>
+      <c r="AG33" s="11" t="n"/>
+      <c r="AH33" s="11" t="n"/>
+      <c r="AI33" s="11" t="n"/>
+      <c r="AJ33" s="11" t="n"/>
+      <c r="AK33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1863,6 +2364,18 @@
       <c r="W34" s="11" t="n"/>
       <c r="X34" s="11" t="n"/>
       <c r="Y34" s="11" t="n"/>
+      <c r="Z34" s="11" t="n"/>
+      <c r="AA34" s="11" t="n"/>
+      <c r="AB34" s="11" t="n"/>
+      <c r="AC34" s="11" t="n"/>
+      <c r="AD34" s="11" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="11" t="n"/>
+      <c r="AG34" s="11" t="n"/>
+      <c r="AH34" s="11" t="n"/>
+      <c r="AI34" s="11" t="n"/>
+      <c r="AJ34" s="11" t="n"/>
+      <c r="AK34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1894,6 +2407,18 @@
       <c r="W35" s="11" t="n"/>
       <c r="X35" s="11" t="n"/>
       <c r="Y35" s="11" t="n"/>
+      <c r="Z35" s="11" t="n"/>
+      <c r="AA35" s="11" t="n"/>
+      <c r="AB35" s="11" t="n"/>
+      <c r="AC35" s="11" t="n"/>
+      <c r="AD35" s="11" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="11" t="n"/>
+      <c r="AG35" s="11" t="n"/>
+      <c r="AH35" s="11" t="n"/>
+      <c r="AI35" s="11" t="n"/>
+      <c r="AJ35" s="11" t="n"/>
+      <c r="AK35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1925,6 +2450,18 @@
       <c r="W36" s="11" t="n"/>
       <c r="X36" s="11" t="n"/>
       <c r="Y36" s="11" t="n"/>
+      <c r="Z36" s="11" t="n"/>
+      <c r="AA36" s="11" t="n"/>
+      <c r="AB36" s="11" t="n"/>
+      <c r="AC36" s="11" t="n"/>
+      <c r="AD36" s="11" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="11" t="n"/>
+      <c r="AG36" s="11" t="n"/>
+      <c r="AH36" s="11" t="n"/>
+      <c r="AI36" s="11" t="n"/>
+      <c r="AJ36" s="11" t="n"/>
+      <c r="AK36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1956,6 +2493,18 @@
       <c r="W37" s="11" t="n"/>
       <c r="X37" s="11" t="n"/>
       <c r="Y37" s="11" t="n"/>
+      <c r="Z37" s="11" t="n"/>
+      <c r="AA37" s="11" t="n"/>
+      <c r="AB37" s="11" t="n"/>
+      <c r="AC37" s="11" t="n"/>
+      <c r="AD37" s="11" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="11" t="n"/>
+      <c r="AG37" s="11" t="n"/>
+      <c r="AH37" s="11" t="n"/>
+      <c r="AI37" s="11" t="n"/>
+      <c r="AJ37" s="11" t="n"/>
+      <c r="AK37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1987,6 +2536,18 @@
       <c r="W38" s="11" t="n"/>
       <c r="X38" s="11" t="n"/>
       <c r="Y38" s="11" t="n"/>
+      <c r="Z38" s="11" t="n"/>
+      <c r="AA38" s="11" t="n"/>
+      <c r="AB38" s="11" t="n"/>
+      <c r="AC38" s="11" t="n"/>
+      <c r="AD38" s="11" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="11" t="n"/>
+      <c r="AG38" s="11" t="n"/>
+      <c r="AH38" s="11" t="n"/>
+      <c r="AI38" s="11" t="n"/>
+      <c r="AJ38" s="11" t="n"/>
+      <c r="AK38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2018,6 +2579,18 @@
       <c r="W39" s="11" t="n"/>
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="11" t="n"/>
+      <c r="Z39" s="11" t="n"/>
+      <c r="AA39" s="11" t="n"/>
+      <c r="AB39" s="11" t="n"/>
+      <c r="AC39" s="11" t="n"/>
+      <c r="AD39" s="11" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="11" t="n"/>
+      <c r="AG39" s="11" t="n"/>
+      <c r="AH39" s="11" t="n"/>
+      <c r="AI39" s="11" t="n"/>
+      <c r="AJ39" s="11" t="n"/>
+      <c r="AK39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2049,6 +2622,18 @@
       <c r="W40" s="11" t="n"/>
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="11" t="n"/>
+      <c r="Z40" s="11" t="n"/>
+      <c r="AA40" s="11" t="n"/>
+      <c r="AB40" s="11" t="n"/>
+      <c r="AC40" s="11" t="n"/>
+      <c r="AD40" s="11" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="11" t="n"/>
+      <c r="AG40" s="11" t="n"/>
+      <c r="AH40" s="11" t="n"/>
+      <c r="AI40" s="11" t="n"/>
+      <c r="AJ40" s="11" t="n"/>
+      <c r="AK40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2080,6 +2665,18 @@
       <c r="W41" s="11" t="n"/>
       <c r="X41" s="11" t="n"/>
       <c r="Y41" s="11" t="n"/>
+      <c r="Z41" s="11" t="n"/>
+      <c r="AA41" s="11" t="n"/>
+      <c r="AB41" s="11" t="n"/>
+      <c r="AC41" s="11" t="n"/>
+      <c r="AD41" s="11" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="11" t="n"/>
+      <c r="AG41" s="11" t="n"/>
+      <c r="AH41" s="11" t="n"/>
+      <c r="AI41" s="11" t="n"/>
+      <c r="AJ41" s="11" t="n"/>
+      <c r="AK41" s="11" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2111,6 +2708,18 @@
       <c r="W42" s="11" t="n"/>
       <c r="X42" s="11" t="n"/>
       <c r="Y42" s="11" t="n"/>
+      <c r="Z42" s="11" t="n"/>
+      <c r="AA42" s="11" t="n"/>
+      <c r="AB42" s="11" t="n"/>
+      <c r="AC42" s="11" t="n"/>
+      <c r="AD42" s="11" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="11" t="n"/>
+      <c r="AG42" s="11" t="n"/>
+      <c r="AH42" s="11" t="n"/>
+      <c r="AI42" s="11" t="n"/>
+      <c r="AJ42" s="11" t="n"/>
+      <c r="AK42" s="11" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2142,6 +2751,18 @@
       <c r="W43" s="11" t="n"/>
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="11" t="n"/>
+      <c r="Z43" s="11" t="n"/>
+      <c r="AA43" s="11" t="n"/>
+      <c r="AB43" s="11" t="n"/>
+      <c r="AC43" s="11" t="n"/>
+      <c r="AD43" s="11" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="11" t="n"/>
+      <c r="AG43" s="11" t="n"/>
+      <c r="AH43" s="11" t="n"/>
+      <c r="AI43" s="11" t="n"/>
+      <c r="AJ43" s="11" t="n"/>
+      <c r="AK43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2173,6 +2794,18 @@
       <c r="W44" s="11" t="n"/>
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="11" t="n"/>
+      <c r="Z44" s="11" t="n"/>
+      <c r="AA44" s="11" t="n"/>
+      <c r="AB44" s="11" t="n"/>
+      <c r="AC44" s="11" t="n"/>
+      <c r="AD44" s="11" t="n"/>
+      <c r="AE44" s="11" t="n"/>
+      <c r="AF44" s="11" t="n"/>
+      <c r="AG44" s="11" t="n"/>
+      <c r="AH44" s="11" t="n"/>
+      <c r="AI44" s="11" t="n"/>
+      <c r="AJ44" s="11" t="n"/>
+      <c r="AK44" s="11" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2204,6 +2837,18 @@
       <c r="W45" s="11" t="n"/>
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="11" t="n"/>
+      <c r="Z45" s="11" t="n"/>
+      <c r="AA45" s="11" t="n"/>
+      <c r="AB45" s="11" t="n"/>
+      <c r="AC45" s="11" t="n"/>
+      <c r="AD45" s="11" t="n"/>
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="11" t="n"/>
+      <c r="AG45" s="11" t="n"/>
+      <c r="AH45" s="11" t="n"/>
+      <c r="AI45" s="11" t="n"/>
+      <c r="AJ45" s="11" t="n"/>
+      <c r="AK45" s="11" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2235,6 +2880,18 @@
       <c r="W46" s="11" t="n"/>
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="11" t="n"/>
+      <c r="Z46" s="11" t="n"/>
+      <c r="AA46" s="11" t="n"/>
+      <c r="AB46" s="11" t="n"/>
+      <c r="AC46" s="11" t="n"/>
+      <c r="AD46" s="11" t="n"/>
+      <c r="AE46" s="11" t="n"/>
+      <c r="AF46" s="11" t="n"/>
+      <c r="AG46" s="11" t="n"/>
+      <c r="AH46" s="11" t="n"/>
+      <c r="AI46" s="11" t="n"/>
+      <c r="AJ46" s="11" t="n"/>
+      <c r="AK46" s="11" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2266,6 +2923,18 @@
       <c r="W47" s="11" t="n"/>
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="11" t="n"/>
+      <c r="Z47" s="11" t="n"/>
+      <c r="AA47" s="11" t="n"/>
+      <c r="AB47" s="11" t="n"/>
+      <c r="AC47" s="11" t="n"/>
+      <c r="AD47" s="11" t="n"/>
+      <c r="AE47" s="11" t="n"/>
+      <c r="AF47" s="11" t="n"/>
+      <c r="AG47" s="11" t="n"/>
+      <c r="AH47" s="11" t="n"/>
+      <c r="AI47" s="11" t="n"/>
+      <c r="AJ47" s="11" t="n"/>
+      <c r="AK47" s="11" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2297,6 +2966,18 @@
       <c r="W48" s="11" t="n"/>
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="11" t="n"/>
+      <c r="Z48" s="11" t="n"/>
+      <c r="AA48" s="11" t="n"/>
+      <c r="AB48" s="11" t="n"/>
+      <c r="AC48" s="11" t="n"/>
+      <c r="AD48" s="11" t="n"/>
+      <c r="AE48" s="11" t="n"/>
+      <c r="AF48" s="11" t="n"/>
+      <c r="AG48" s="11" t="n"/>
+      <c r="AH48" s="11" t="n"/>
+      <c r="AI48" s="11" t="n"/>
+      <c r="AJ48" s="11" t="n"/>
+      <c r="AK48" s="11" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2328,6 +3009,18 @@
       <c r="W49" s="11" t="n"/>
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="11" t="n"/>
+      <c r="Z49" s="11" t="n"/>
+      <c r="AA49" s="11" t="n"/>
+      <c r="AB49" s="11" t="n"/>
+      <c r="AC49" s="11" t="n"/>
+      <c r="AD49" s="11" t="n"/>
+      <c r="AE49" s="11" t="n"/>
+      <c r="AF49" s="11" t="n"/>
+      <c r="AG49" s="11" t="n"/>
+      <c r="AH49" s="11" t="n"/>
+      <c r="AI49" s="11" t="n"/>
+      <c r="AJ49" s="11" t="n"/>
+      <c r="AK49" s="11" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2359,6 +3052,18 @@
       <c r="W50" s="11" t="n"/>
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="11" t="n"/>
+      <c r="Z50" s="11" t="n"/>
+      <c r="AA50" s="11" t="n"/>
+      <c r="AB50" s="11" t="n"/>
+      <c r="AC50" s="11" t="n"/>
+      <c r="AD50" s="11" t="n"/>
+      <c r="AE50" s="11" t="n"/>
+      <c r="AF50" s="11" t="n"/>
+      <c r="AG50" s="11" t="n"/>
+      <c r="AH50" s="11" t="n"/>
+      <c r="AI50" s="11" t="n"/>
+      <c r="AJ50" s="11" t="n"/>
+      <c r="AK50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2390,6 +3095,18 @@
       <c r="W51" s="11" t="n"/>
       <c r="X51" s="11" t="n"/>
       <c r="Y51" s="11" t="n"/>
+      <c r="Z51" s="11" t="n"/>
+      <c r="AA51" s="11" t="n"/>
+      <c r="AB51" s="11" t="n"/>
+      <c r="AC51" s="11" t="n"/>
+      <c r="AD51" s="11" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="11" t="n"/>
+      <c r="AG51" s="11" t="n"/>
+      <c r="AH51" s="11" t="n"/>
+      <c r="AI51" s="11" t="n"/>
+      <c r="AJ51" s="11" t="n"/>
+      <c r="AK51" s="11" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2421,6 +3138,18 @@
       <c r="W52" s="11" t="n"/>
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="11" t="n"/>
+      <c r="Z52" s="11" t="n"/>
+      <c r="AA52" s="11" t="n"/>
+      <c r="AB52" s="11" t="n"/>
+      <c r="AC52" s="11" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="11" t="n"/>
+      <c r="AH52" s="11" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="11" t="n"/>
+      <c r="AK52" s="11" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2452,6 +3181,18 @@
       <c r="W53" s="11" t="n"/>
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="11" t="n"/>
+      <c r="Z53" s="11" t="n"/>
+      <c r="AA53" s="11" t="n"/>
+      <c r="AB53" s="11" t="n"/>
+      <c r="AC53" s="11" t="n"/>
+      <c r="AD53" s="11" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="11" t="n"/>
+      <c r="AG53" s="11" t="n"/>
+      <c r="AH53" s="11" t="n"/>
+      <c r="AI53" s="11" t="n"/>
+      <c r="AJ53" s="11" t="n"/>
+      <c r="AK53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2483,6 +3224,18 @@
       <c r="W54" s="11" t="n"/>
       <c r="X54" s="11" t="n"/>
       <c r="Y54" s="11" t="n"/>
+      <c r="Z54" s="11" t="n"/>
+      <c r="AA54" s="11" t="n"/>
+      <c r="AB54" s="11" t="n"/>
+      <c r="AC54" s="11" t="n"/>
+      <c r="AD54" s="11" t="n"/>
+      <c r="AE54" s="11" t="n"/>
+      <c r="AF54" s="11" t="n"/>
+      <c r="AG54" s="11" t="n"/>
+      <c r="AH54" s="11" t="n"/>
+      <c r="AI54" s="11" t="n"/>
+      <c r="AJ54" s="11" t="n"/>
+      <c r="AK54" s="11" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2514,6 +3267,18 @@
       <c r="W55" s="11" t="n"/>
       <c r="X55" s="11" t="n"/>
       <c r="Y55" s="11" t="n"/>
+      <c r="Z55" s="11" t="n"/>
+      <c r="AA55" s="11" t="n"/>
+      <c r="AB55" s="11" t="n"/>
+      <c r="AC55" s="11" t="n"/>
+      <c r="AD55" s="11" t="n"/>
+      <c r="AE55" s="11" t="n"/>
+      <c r="AF55" s="11" t="n"/>
+      <c r="AG55" s="11" t="n"/>
+      <c r="AH55" s="11" t="n"/>
+      <c r="AI55" s="11" t="n"/>
+      <c r="AJ55" s="11" t="n"/>
+      <c r="AK55" s="11" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -2545,6 +3310,18 @@
       <c r="W56" s="11" t="n"/>
       <c r="X56" s="11" t="n"/>
       <c r="Y56" s="11" t="n"/>
+      <c r="Z56" s="11" t="n"/>
+      <c r="AA56" s="11" t="n"/>
+      <c r="AB56" s="11" t="n"/>
+      <c r="AC56" s="11" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+      <c r="AE56" s="11" t="n"/>
+      <c r="AF56" s="11" t="n"/>
+      <c r="AG56" s="11" t="n"/>
+      <c r="AH56" s="11" t="n"/>
+      <c r="AI56" s="11" t="n"/>
+      <c r="AJ56" s="11" t="n"/>
+      <c r="AK56" s="11" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2576,6 +3353,18 @@
       <c r="W57" s="11" t="n"/>
       <c r="X57" s="11" t="n"/>
       <c r="Y57" s="11" t="n"/>
+      <c r="Z57" s="11" t="n"/>
+      <c r="AA57" s="11" t="n"/>
+      <c r="AB57" s="11" t="n"/>
+      <c r="AC57" s="11" t="n"/>
+      <c r="AD57" s="11" t="n"/>
+      <c r="AE57" s="11" t="n"/>
+      <c r="AF57" s="11" t="n"/>
+      <c r="AG57" s="11" t="n"/>
+      <c r="AH57" s="11" t="n"/>
+      <c r="AI57" s="11" t="n"/>
+      <c r="AJ57" s="11" t="n"/>
+      <c r="AK57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -2607,6 +3396,18 @@
       <c r="W58" s="11" t="n"/>
       <c r="X58" s="11" t="n"/>
       <c r="Y58" s="11" t="n"/>
+      <c r="Z58" s="11" t="n"/>
+      <c r="AA58" s="11" t="n"/>
+      <c r="AB58" s="11" t="n"/>
+      <c r="AC58" s="11" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="11" t="n"/>
+      <c r="AF58" s="11" t="n"/>
+      <c r="AG58" s="11" t="n"/>
+      <c r="AH58" s="11" t="n"/>
+      <c r="AI58" s="11" t="n"/>
+      <c r="AJ58" s="11" t="n"/>
+      <c r="AK58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2638,6 +3439,18 @@
       <c r="W59" s="11" t="n"/>
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="11" t="n"/>
+      <c r="Z59" s="11" t="n"/>
+      <c r="AA59" s="11" t="n"/>
+      <c r="AB59" s="11" t="n"/>
+      <c r="AC59" s="11" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="11" t="n"/>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="11" t="n"/>
+      <c r="AH59" s="11" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="11" t="n"/>
+      <c r="AK59" s="11" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -2669,6 +3482,18 @@
       <c r="W60" s="11" t="n"/>
       <c r="X60" s="11" t="n"/>
       <c r="Y60" s="11" t="n"/>
+      <c r="Z60" s="11" t="n"/>
+      <c r="AA60" s="11" t="n"/>
+      <c r="AB60" s="11" t="n"/>
+      <c r="AC60" s="11" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="11" t="n"/>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="11" t="n"/>
+      <c r="AH60" s="11" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="11" t="n"/>
+      <c r="AK60" s="11" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -2700,6 +3525,18 @@
       <c r="W61" s="11" t="n"/>
       <c r="X61" s="11" t="n"/>
       <c r="Y61" s="11" t="n"/>
+      <c r="Z61" s="11" t="n"/>
+      <c r="AA61" s="11" t="n"/>
+      <c r="AB61" s="11" t="n"/>
+      <c r="AC61" s="11" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="11" t="n"/>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="11" t="n"/>
+      <c r="AH61" s="11" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="11" t="n"/>
+      <c r="AK61" s="11" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -2731,6 +3568,18 @@
       <c r="W62" s="11" t="n"/>
       <c r="X62" s="11" t="n"/>
       <c r="Y62" s="11" t="n"/>
+      <c r="Z62" s="11" t="n"/>
+      <c r="AA62" s="11" t="n"/>
+      <c r="AB62" s="11" t="n"/>
+      <c r="AC62" s="11" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+      <c r="AE62" s="11" t="n"/>
+      <c r="AF62" s="11" t="n"/>
+      <c r="AG62" s="11" t="n"/>
+      <c r="AH62" s="11" t="n"/>
+      <c r="AI62" s="11" t="n"/>
+      <c r="AJ62" s="11" t="n"/>
+      <c r="AK62" s="11" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -2762,6 +3611,18 @@
       <c r="W63" s="11" t="n"/>
       <c r="X63" s="11" t="n"/>
       <c r="Y63" s="11" t="n"/>
+      <c r="Z63" s="11" t="n"/>
+      <c r="AA63" s="11" t="n"/>
+      <c r="AB63" s="11" t="n"/>
+      <c r="AC63" s="11" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+      <c r="AE63" s="11" t="n"/>
+      <c r="AF63" s="11" t="n"/>
+      <c r="AG63" s="11" t="n"/>
+      <c r="AH63" s="11" t="n"/>
+      <c r="AI63" s="11" t="n"/>
+      <c r="AJ63" s="11" t="n"/>
+      <c r="AK63" s="11" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2793,6 +3654,18 @@
       <c r="W64" s="11" t="n"/>
       <c r="X64" s="11" t="n"/>
       <c r="Y64" s="11" t="n"/>
+      <c r="Z64" s="11" t="n"/>
+      <c r="AA64" s="11" t="n"/>
+      <c r="AB64" s="11" t="n"/>
+      <c r="AC64" s="11" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="11" t="n"/>
+      <c r="AF64" s="11" t="n"/>
+      <c r="AG64" s="11" t="n"/>
+      <c r="AH64" s="11" t="n"/>
+      <c r="AI64" s="11" t="n"/>
+      <c r="AJ64" s="11" t="n"/>
+      <c r="AK64" s="11" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -2824,6 +3697,18 @@
       <c r="W65" s="11" t="n"/>
       <c r="X65" s="11" t="n"/>
       <c r="Y65" s="11" t="n"/>
+      <c r="Z65" s="11" t="n"/>
+      <c r="AA65" s="11" t="n"/>
+      <c r="AB65" s="11" t="n"/>
+      <c r="AC65" s="11" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="11" t="n"/>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="11" t="n"/>
+      <c r="AH65" s="11" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="11" t="n"/>
+      <c r="AK65" s="11" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -2855,6 +3740,18 @@
       <c r="W66" s="11" t="n"/>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n"/>
+      <c r="Z66" s="11" t="n"/>
+      <c r="AA66" s="11" t="n"/>
+      <c r="AB66" s="11" t="n"/>
+      <c r="AC66" s="11" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="11" t="n"/>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="11" t="n"/>
+      <c r="AH66" s="11" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="11" t="n"/>
+      <c r="AK66" s="11" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -2886,6 +3783,18 @@
       <c r="W67" s="11" t="n"/>
       <c r="X67" s="11" t="n"/>
       <c r="Y67" s="11" t="n"/>
+      <c r="Z67" s="11" t="n"/>
+      <c r="AA67" s="11" t="n"/>
+      <c r="AB67" s="11" t="n"/>
+      <c r="AC67" s="11" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="11" t="n"/>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="11" t="n"/>
+      <c r="AH67" s="11" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="11" t="n"/>
+      <c r="AK67" s="11" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -2917,6 +3826,18 @@
       <c r="W68" s="11" t="n"/>
       <c r="X68" s="11" t="n"/>
       <c r="Y68" s="11" t="n"/>
+      <c r="Z68" s="11" t="n"/>
+      <c r="AA68" s="11" t="n"/>
+      <c r="AB68" s="11" t="n"/>
+      <c r="AC68" s="11" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="11" t="n"/>
+      <c r="AF68" s="11" t="n"/>
+      <c r="AG68" s="11" t="n"/>
+      <c r="AH68" s="11" t="n"/>
+      <c r="AI68" s="11" t="n"/>
+      <c r="AJ68" s="11" t="n"/>
+      <c r="AK68" s="11" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -2948,6 +3869,18 @@
       <c r="W69" s="11" t="n"/>
       <c r="X69" s="11" t="n"/>
       <c r="Y69" s="11" t="n"/>
+      <c r="Z69" s="11" t="n"/>
+      <c r="AA69" s="11" t="n"/>
+      <c r="AB69" s="11" t="n"/>
+      <c r="AC69" s="11" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="11" t="n"/>
+      <c r="AF69" s="11" t="n"/>
+      <c r="AG69" s="11" t="n"/>
+      <c r="AH69" s="11" t="n"/>
+      <c r="AI69" s="11" t="n"/>
+      <c r="AJ69" s="11" t="n"/>
+      <c r="AK69" s="11" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -2979,6 +3912,18 @@
       <c r="W70" s="11" t="n"/>
       <c r="X70" s="11" t="n"/>
       <c r="Y70" s="11" t="n"/>
+      <c r="Z70" s="11" t="n"/>
+      <c r="AA70" s="11" t="n"/>
+      <c r="AB70" s="11" t="n"/>
+      <c r="AC70" s="11" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="11" t="n"/>
+      <c r="AF70" s="11" t="n"/>
+      <c r="AG70" s="11" t="n"/>
+      <c r="AH70" s="11" t="n"/>
+      <c r="AI70" s="11" t="n"/>
+      <c r="AJ70" s="11" t="n"/>
+      <c r="AK70" s="11" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -3010,6 +3955,18 @@
       <c r="W71" s="11" t="n"/>
       <c r="X71" s="11" t="n"/>
       <c r="Y71" s="11" t="n"/>
+      <c r="Z71" s="11" t="n"/>
+      <c r="AA71" s="11" t="n"/>
+      <c r="AB71" s="11" t="n"/>
+      <c r="AC71" s="11" t="n"/>
+      <c r="AD71" s="11" t="n"/>
+      <c r="AE71" s="11" t="n"/>
+      <c r="AF71" s="11" t="n"/>
+      <c r="AG71" s="11" t="n"/>
+      <c r="AH71" s="11" t="n"/>
+      <c r="AI71" s="11" t="n"/>
+      <c r="AJ71" s="11" t="n"/>
+      <c r="AK71" s="11" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -3041,6 +3998,18 @@
       <c r="W72" s="11" t="n"/>
       <c r="X72" s="11" t="n"/>
       <c r="Y72" s="11" t="n"/>
+      <c r="Z72" s="11" t="n"/>
+      <c r="AA72" s="11" t="n"/>
+      <c r="AB72" s="11" t="n"/>
+      <c r="AC72" s="11" t="n"/>
+      <c r="AD72" s="11" t="n"/>
+      <c r="AE72" s="11" t="n"/>
+      <c r="AF72" s="11" t="n"/>
+      <c r="AG72" s="11" t="n"/>
+      <c r="AH72" s="11" t="n"/>
+      <c r="AI72" s="11" t="n"/>
+      <c r="AJ72" s="11" t="n"/>
+      <c r="AK72" s="11" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3072,6 +4041,18 @@
       <c r="W73" s="11" t="n"/>
       <c r="X73" s="11" t="n"/>
       <c r="Y73" s="11" t="n"/>
+      <c r="Z73" s="11" t="n"/>
+      <c r="AA73" s="11" t="n"/>
+      <c r="AB73" s="11" t="n"/>
+      <c r="AC73" s="11" t="n"/>
+      <c r="AD73" s="11" t="n"/>
+      <c r="AE73" s="11" t="n"/>
+      <c r="AF73" s="11" t="n"/>
+      <c r="AG73" s="11" t="n"/>
+      <c r="AH73" s="11" t="n"/>
+      <c r="AI73" s="11" t="n"/>
+      <c r="AJ73" s="11" t="n"/>
+      <c r="AK73" s="11" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3103,6 +4084,18 @@
       <c r="W74" s="11" t="n"/>
       <c r="X74" s="11" t="n"/>
       <c r="Y74" s="11" t="n"/>
+      <c r="Z74" s="11" t="n"/>
+      <c r="AA74" s="11" t="n"/>
+      <c r="AB74" s="11" t="n"/>
+      <c r="AC74" s="11" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+      <c r="AE74" s="11" t="n"/>
+      <c r="AF74" s="11" t="n"/>
+      <c r="AG74" s="11" t="n"/>
+      <c r="AH74" s="11" t="n"/>
+      <c r="AI74" s="11" t="n"/>
+      <c r="AJ74" s="11" t="n"/>
+      <c r="AK74" s="11" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -3134,6 +4127,18 @@
       <c r="W75" s="11" t="n"/>
       <c r="X75" s="11" t="n"/>
       <c r="Y75" s="11" t="n"/>
+      <c r="Z75" s="11" t="n"/>
+      <c r="AA75" s="11" t="n"/>
+      <c r="AB75" s="11" t="n"/>
+      <c r="AC75" s="11" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+      <c r="AE75" s="11" t="n"/>
+      <c r="AF75" s="11" t="n"/>
+      <c r="AG75" s="11" t="n"/>
+      <c r="AH75" s="11" t="n"/>
+      <c r="AI75" s="11" t="n"/>
+      <c r="AJ75" s="11" t="n"/>
+      <c r="AK75" s="11" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3165,6 +4170,18 @@
       <c r="W76" s="11" t="n"/>
       <c r="X76" s="11" t="n"/>
       <c r="Y76" s="11" t="n"/>
+      <c r="Z76" s="11" t="n"/>
+      <c r="AA76" s="11" t="n"/>
+      <c r="AB76" s="11" t="n"/>
+      <c r="AC76" s="11" t="n"/>
+      <c r="AD76" s="11" t="n"/>
+      <c r="AE76" s="11" t="n"/>
+      <c r="AF76" s="11" t="n"/>
+      <c r="AG76" s="11" t="n"/>
+      <c r="AH76" s="11" t="n"/>
+      <c r="AI76" s="11" t="n"/>
+      <c r="AJ76" s="11" t="n"/>
+      <c r="AK76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -3196,6 +4213,18 @@
       <c r="W77" s="11" t="n"/>
       <c r="X77" s="11" t="n"/>
       <c r="Y77" s="11" t="n"/>
+      <c r="Z77" s="11" t="n"/>
+      <c r="AA77" s="11" t="n"/>
+      <c r="AB77" s="11" t="n"/>
+      <c r="AC77" s="11" t="n"/>
+      <c r="AD77" s="11" t="n"/>
+      <c r="AE77" s="11" t="n"/>
+      <c r="AF77" s="11" t="n"/>
+      <c r="AG77" s="11" t="n"/>
+      <c r="AH77" s="11" t="n"/>
+      <c r="AI77" s="11" t="n"/>
+      <c r="AJ77" s="11" t="n"/>
+      <c r="AK77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -3227,6 +4256,18 @@
       <c r="W78" s="11" t="n"/>
       <c r="X78" s="11" t="n"/>
       <c r="Y78" s="11" t="n"/>
+      <c r="Z78" s="11" t="n"/>
+      <c r="AA78" s="11" t="n"/>
+      <c r="AB78" s="11" t="n"/>
+      <c r="AC78" s="11" t="n"/>
+      <c r="AD78" s="11" t="n"/>
+      <c r="AE78" s="11" t="n"/>
+      <c r="AF78" s="11" t="n"/>
+      <c r="AG78" s="11" t="n"/>
+      <c r="AH78" s="11" t="n"/>
+      <c r="AI78" s="11" t="n"/>
+      <c r="AJ78" s="11" t="n"/>
+      <c r="AK78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -3258,6 +4299,18 @@
       <c r="W79" s="11" t="n"/>
       <c r="X79" s="11" t="n"/>
       <c r="Y79" s="11" t="n"/>
+      <c r="Z79" s="11" t="n"/>
+      <c r="AA79" s="11" t="n"/>
+      <c r="AB79" s="11" t="n"/>
+      <c r="AC79" s="11" t="n"/>
+      <c r="AD79" s="11" t="n"/>
+      <c r="AE79" s="11" t="n"/>
+      <c r="AF79" s="11" t="n"/>
+      <c r="AG79" s="11" t="n"/>
+      <c r="AH79" s="11" t="n"/>
+      <c r="AI79" s="11" t="n"/>
+      <c r="AJ79" s="11" t="n"/>
+      <c r="AK79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -3289,6 +4342,18 @@
       <c r="W80" s="11" t="n"/>
       <c r="X80" s="11" t="n"/>
       <c r="Y80" s="11" t="n"/>
+      <c r="Z80" s="11" t="n"/>
+      <c r="AA80" s="11" t="n"/>
+      <c r="AB80" s="11" t="n"/>
+      <c r="AC80" s="11" t="n"/>
+      <c r="AD80" s="11" t="n"/>
+      <c r="AE80" s="11" t="n"/>
+      <c r="AF80" s="11" t="n"/>
+      <c r="AG80" s="11" t="n"/>
+      <c r="AH80" s="11" t="n"/>
+      <c r="AI80" s="11" t="n"/>
+      <c r="AJ80" s="11" t="n"/>
+      <c r="AK80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -3320,6 +4385,18 @@
       <c r="W81" s="11" t="n"/>
       <c r="X81" s="11" t="n"/>
       <c r="Y81" s="11" t="n"/>
+      <c r="Z81" s="11" t="n"/>
+      <c r="AA81" s="11" t="n"/>
+      <c r="AB81" s="11" t="n"/>
+      <c r="AC81" s="11" t="n"/>
+      <c r="AD81" s="11" t="n"/>
+      <c r="AE81" s="11" t="n"/>
+      <c r="AF81" s="11" t="n"/>
+      <c r="AG81" s="11" t="n"/>
+      <c r="AH81" s="11" t="n"/>
+      <c r="AI81" s="11" t="n"/>
+      <c r="AJ81" s="11" t="n"/>
+      <c r="AK81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -3351,6 +4428,18 @@
       <c r="W82" s="11" t="n"/>
       <c r="X82" s="11" t="n"/>
       <c r="Y82" s="11" t="n"/>
+      <c r="Z82" s="11" t="n"/>
+      <c r="AA82" s="11" t="n"/>
+      <c r="AB82" s="11" t="n"/>
+      <c r="AC82" s="11" t="n"/>
+      <c r="AD82" s="11" t="n"/>
+      <c r="AE82" s="11" t="n"/>
+      <c r="AF82" s="11" t="n"/>
+      <c r="AG82" s="11" t="n"/>
+      <c r="AH82" s="11" t="n"/>
+      <c r="AI82" s="11" t="n"/>
+      <c r="AJ82" s="11" t="n"/>
+      <c r="AK82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -3382,6 +4471,18 @@
       <c r="W83" s="11" t="n"/>
       <c r="X83" s="11" t="n"/>
       <c r="Y83" s="11" t="n"/>
+      <c r="Z83" s="11" t="n"/>
+      <c r="AA83" s="11" t="n"/>
+      <c r="AB83" s="11" t="n"/>
+      <c r="AC83" s="11" t="n"/>
+      <c r="AD83" s="11" t="n"/>
+      <c r="AE83" s="11" t="n"/>
+      <c r="AF83" s="11" t="n"/>
+      <c r="AG83" s="11" t="n"/>
+      <c r="AH83" s="11" t="n"/>
+      <c r="AI83" s="11" t="n"/>
+      <c r="AJ83" s="11" t="n"/>
+      <c r="AK83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -3413,6 +4514,18 @@
       <c r="W84" s="11" t="n"/>
       <c r="X84" s="11" t="n"/>
       <c r="Y84" s="11" t="n"/>
+      <c r="Z84" s="11" t="n"/>
+      <c r="AA84" s="11" t="n"/>
+      <c r="AB84" s="11" t="n"/>
+      <c r="AC84" s="11" t="n"/>
+      <c r="AD84" s="11" t="n"/>
+      <c r="AE84" s="11" t="n"/>
+      <c r="AF84" s="11" t="n"/>
+      <c r="AG84" s="11" t="n"/>
+      <c r="AH84" s="11" t="n"/>
+      <c r="AI84" s="11" t="n"/>
+      <c r="AJ84" s="11" t="n"/>
+      <c r="AK84" s="11" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -3444,6 +4557,18 @@
       <c r="W85" s="11" t="n"/>
       <c r="X85" s="11" t="n"/>
       <c r="Y85" s="11" t="n"/>
+      <c r="Z85" s="11" t="n"/>
+      <c r="AA85" s="11" t="n"/>
+      <c r="AB85" s="11" t="n"/>
+      <c r="AC85" s="11" t="n"/>
+      <c r="AD85" s="11" t="n"/>
+      <c r="AE85" s="11" t="n"/>
+      <c r="AF85" s="11" t="n"/>
+      <c r="AG85" s="11" t="n"/>
+      <c r="AH85" s="11" t="n"/>
+      <c r="AI85" s="11" t="n"/>
+      <c r="AJ85" s="11" t="n"/>
+      <c r="AK85" s="11" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -3475,6 +4600,18 @@
       <c r="W86" s="11" t="n"/>
       <c r="X86" s="11" t="n"/>
       <c r="Y86" s="11" t="n"/>
+      <c r="Z86" s="11" t="n"/>
+      <c r="AA86" s="11" t="n"/>
+      <c r="AB86" s="11" t="n"/>
+      <c r="AC86" s="11" t="n"/>
+      <c r="AD86" s="11" t="n"/>
+      <c r="AE86" s="11" t="n"/>
+      <c r="AF86" s="11" t="n"/>
+      <c r="AG86" s="11" t="n"/>
+      <c r="AH86" s="11" t="n"/>
+      <c r="AI86" s="11" t="n"/>
+      <c r="AJ86" s="11" t="n"/>
+      <c r="AK86" s="11" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -3506,6 +4643,18 @@
       <c r="W87" s="11" t="n"/>
       <c r="X87" s="11" t="n"/>
       <c r="Y87" s="11" t="n"/>
+      <c r="Z87" s="11" t="n"/>
+      <c r="AA87" s="11" t="n"/>
+      <c r="AB87" s="11" t="n"/>
+      <c r="AC87" s="11" t="n"/>
+      <c r="AD87" s="11" t="n"/>
+      <c r="AE87" s="11" t="n"/>
+      <c r="AF87" s="11" t="n"/>
+      <c r="AG87" s="11" t="n"/>
+      <c r="AH87" s="11" t="n"/>
+      <c r="AI87" s="11" t="n"/>
+      <c r="AJ87" s="11" t="n"/>
+      <c r="AK87" s="11" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -3537,6 +4686,18 @@
       <c r="W88" s="11" t="n"/>
       <c r="X88" s="11" t="n"/>
       <c r="Y88" s="11" t="n"/>
+      <c r="Z88" s="11" t="n"/>
+      <c r="AA88" s="11" t="n"/>
+      <c r="AB88" s="11" t="n"/>
+      <c r="AC88" s="11" t="n"/>
+      <c r="AD88" s="11" t="n"/>
+      <c r="AE88" s="11" t="n"/>
+      <c r="AF88" s="11" t="n"/>
+      <c r="AG88" s="11" t="n"/>
+      <c r="AH88" s="11" t="n"/>
+      <c r="AI88" s="11" t="n"/>
+      <c r="AJ88" s="11" t="n"/>
+      <c r="AK88" s="11" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -3568,6 +4729,18 @@
       <c r="W89" s="11" t="n"/>
       <c r="X89" s="11" t="n"/>
       <c r="Y89" s="11" t="n"/>
+      <c r="Z89" s="11" t="n"/>
+      <c r="AA89" s="11" t="n"/>
+      <c r="AB89" s="11" t="n"/>
+      <c r="AC89" s="11" t="n"/>
+      <c r="AD89" s="11" t="n"/>
+      <c r="AE89" s="11" t="n"/>
+      <c r="AF89" s="11" t="n"/>
+      <c r="AG89" s="11" t="n"/>
+      <c r="AH89" s="11" t="n"/>
+      <c r="AI89" s="11" t="n"/>
+      <c r="AJ89" s="11" t="n"/>
+      <c r="AK89" s="11" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -3599,6 +4772,18 @@
       <c r="W90" s="11" t="n"/>
       <c r="X90" s="11" t="n"/>
       <c r="Y90" s="11" t="n"/>
+      <c r="Z90" s="11" t="n"/>
+      <c r="AA90" s="11" t="n"/>
+      <c r="AB90" s="11" t="n"/>
+      <c r="AC90" s="11" t="n"/>
+      <c r="AD90" s="11" t="n"/>
+      <c r="AE90" s="11" t="n"/>
+      <c r="AF90" s="11" t="n"/>
+      <c r="AG90" s="11" t="n"/>
+      <c r="AH90" s="11" t="n"/>
+      <c r="AI90" s="11" t="n"/>
+      <c r="AJ90" s="11" t="n"/>
+      <c r="AK90" s="11" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -3630,6 +4815,18 @@
       <c r="W91" s="11" t="n"/>
       <c r="X91" s="11" t="n"/>
       <c r="Y91" s="11" t="n"/>
+      <c r="Z91" s="11" t="n"/>
+      <c r="AA91" s="11" t="n"/>
+      <c r="AB91" s="11" t="n"/>
+      <c r="AC91" s="11" t="n"/>
+      <c r="AD91" s="11" t="n"/>
+      <c r="AE91" s="11" t="n"/>
+      <c r="AF91" s="11" t="n"/>
+      <c r="AG91" s="11" t="n"/>
+      <c r="AH91" s="11" t="n"/>
+      <c r="AI91" s="11" t="n"/>
+      <c r="AJ91" s="11" t="n"/>
+      <c r="AK91" s="11" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -3661,6 +4858,18 @@
       <c r="W92" s="11" t="n"/>
       <c r="X92" s="11" t="n"/>
       <c r="Y92" s="11" t="n"/>
+      <c r="Z92" s="11" t="n"/>
+      <c r="AA92" s="11" t="n"/>
+      <c r="AB92" s="11" t="n"/>
+      <c r="AC92" s="11" t="n"/>
+      <c r="AD92" s="11" t="n"/>
+      <c r="AE92" s="11" t="n"/>
+      <c r="AF92" s="11" t="n"/>
+      <c r="AG92" s="11" t="n"/>
+      <c r="AH92" s="11" t="n"/>
+      <c r="AI92" s="11" t="n"/>
+      <c r="AJ92" s="11" t="n"/>
+      <c r="AK92" s="11" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -3692,6 +4901,18 @@
       <c r="W93" s="11" t="n"/>
       <c r="X93" s="11" t="n"/>
       <c r="Y93" s="11" t="n"/>
+      <c r="Z93" s="11" t="n"/>
+      <c r="AA93" s="11" t="n"/>
+      <c r="AB93" s="11" t="n"/>
+      <c r="AC93" s="11" t="n"/>
+      <c r="AD93" s="11" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+      <c r="AF93" s="11" t="n"/>
+      <c r="AG93" s="11" t="n"/>
+      <c r="AH93" s="11" t="n"/>
+      <c r="AI93" s="11" t="n"/>
+      <c r="AJ93" s="11" t="n"/>
+      <c r="AK93" s="11" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -3723,6 +4944,18 @@
       <c r="W94" s="11" t="n"/>
       <c r="X94" s="11" t="n"/>
       <c r="Y94" s="11" t="n"/>
+      <c r="Z94" s="11" t="n"/>
+      <c r="AA94" s="11" t="n"/>
+      <c r="AB94" s="11" t="n"/>
+      <c r="AC94" s="11" t="n"/>
+      <c r="AD94" s="11" t="n"/>
+      <c r="AE94" s="11" t="n"/>
+      <c r="AF94" s="11" t="n"/>
+      <c r="AG94" s="11" t="n"/>
+      <c r="AH94" s="11" t="n"/>
+      <c r="AI94" s="11" t="n"/>
+      <c r="AJ94" s="11" t="n"/>
+      <c r="AK94" s="11" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -3754,6 +4987,18 @@
       <c r="W95" s="11" t="n"/>
       <c r="X95" s="11" t="n"/>
       <c r="Y95" s="11" t="n"/>
+      <c r="Z95" s="11" t="n"/>
+      <c r="AA95" s="11" t="n"/>
+      <c r="AB95" s="11" t="n"/>
+      <c r="AC95" s="11" t="n"/>
+      <c r="AD95" s="11" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="11" t="n"/>
+      <c r="AG95" s="11" t="n"/>
+      <c r="AH95" s="11" t="n"/>
+      <c r="AI95" s="11" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="11" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -3785,6 +5030,18 @@
       <c r="W96" s="11" t="n"/>
       <c r="X96" s="11" t="n"/>
       <c r="Y96" s="11" t="n"/>
+      <c r="Z96" s="11" t="n"/>
+      <c r="AA96" s="11" t="n"/>
+      <c r="AB96" s="11" t="n"/>
+      <c r="AC96" s="11" t="n"/>
+      <c r="AD96" s="11" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="11" t="n"/>
+      <c r="AG96" s="11" t="n"/>
+      <c r="AH96" s="11" t="n"/>
+      <c r="AI96" s="11" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="11" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -3816,6 +5073,18 @@
       <c r="W97" s="11" t="n"/>
       <c r="X97" s="11" t="n"/>
       <c r="Y97" s="11" t="n"/>
+      <c r="Z97" s="11" t="n"/>
+      <c r="AA97" s="11" t="n"/>
+      <c r="AB97" s="11" t="n"/>
+      <c r="AC97" s="11" t="n"/>
+      <c r="AD97" s="11" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="11" t="n"/>
+      <c r="AG97" s="11" t="n"/>
+      <c r="AH97" s="11" t="n"/>
+      <c r="AI97" s="11" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="11" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -3847,6 +5116,18 @@
       <c r="W98" s="11" t="n"/>
       <c r="X98" s="11" t="n"/>
       <c r="Y98" s="11" t="n"/>
+      <c r="Z98" s="11" t="n"/>
+      <c r="AA98" s="11" t="n"/>
+      <c r="AB98" s="11" t="n"/>
+      <c r="AC98" s="11" t="n"/>
+      <c r="AD98" s="11" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="11" t="n"/>
+      <c r="AG98" s="11" t="n"/>
+      <c r="AH98" s="11" t="n"/>
+      <c r="AI98" s="11" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="11" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -3878,6 +5159,18 @@
       <c r="W99" s="11" t="n"/>
       <c r="X99" s="11" t="n"/>
       <c r="Y99" s="11" t="n"/>
+      <c r="Z99" s="11" t="n"/>
+      <c r="AA99" s="11" t="n"/>
+      <c r="AB99" s="11" t="n"/>
+      <c r="AC99" s="11" t="n"/>
+      <c r="AD99" s="11" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="11" t="n"/>
+      <c r="AG99" s="11" t="n"/>
+      <c r="AH99" s="11" t="n"/>
+      <c r="AI99" s="11" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="11" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -3909,6 +5202,18 @@
       <c r="W100" s="11" t="n"/>
       <c r="X100" s="11" t="n"/>
       <c r="Y100" s="11" t="n"/>
+      <c r="Z100" s="11" t="n"/>
+      <c r="AA100" s="11" t="n"/>
+      <c r="AB100" s="11" t="n"/>
+      <c r="AC100" s="11" t="n"/>
+      <c r="AD100" s="11" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="11" t="n"/>
+      <c r="AG100" s="11" t="n"/>
+      <c r="AH100" s="11" t="n"/>
+      <c r="AI100" s="11" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="11" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -3940,6 +5245,18 @@
       <c r="W101" s="11" t="n"/>
       <c r="X101" s="11" t="n"/>
       <c r="Y101" s="11" t="n"/>
+      <c r="Z101" s="11" t="n"/>
+      <c r="AA101" s="11" t="n"/>
+      <c r="AB101" s="11" t="n"/>
+      <c r="AC101" s="11" t="n"/>
+      <c r="AD101" s="11" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="11" t="n"/>
+      <c r="AG101" s="11" t="n"/>
+      <c r="AH101" s="11" t="n"/>
+      <c r="AI101" s="11" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="11" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -3971,6 +5288,18 @@
       <c r="W102" s="11" t="n"/>
       <c r="X102" s="11" t="n"/>
       <c r="Y102" s="11" t="n"/>
+      <c r="Z102" s="11" t="n"/>
+      <c r="AA102" s="11" t="n"/>
+      <c r="AB102" s="11" t="n"/>
+      <c r="AC102" s="11" t="n"/>
+      <c r="AD102" s="11" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="11" t="n"/>
+      <c r="AG102" s="11" t="n"/>
+      <c r="AH102" s="11" t="n"/>
+      <c r="AI102" s="11" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="11" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -4002,6 +5331,18 @@
       <c r="W103" s="11" t="n"/>
       <c r="X103" s="11" t="n"/>
       <c r="Y103" s="11" t="n"/>
+      <c r="Z103" s="11" t="n"/>
+      <c r="AA103" s="11" t="n"/>
+      <c r="AB103" s="11" t="n"/>
+      <c r="AC103" s="11" t="n"/>
+      <c r="AD103" s="11" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="11" t="n"/>
+      <c r="AG103" s="11" t="n"/>
+      <c r="AH103" s="11" t="n"/>
+      <c r="AI103" s="11" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="11" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -4033,6 +5374,18 @@
       <c r="W104" s="11" t="n"/>
       <c r="X104" s="11" t="n"/>
       <c r="Y104" s="11" t="n"/>
+      <c r="Z104" s="11" t="n"/>
+      <c r="AA104" s="11" t="n"/>
+      <c r="AB104" s="11" t="n"/>
+      <c r="AC104" s="11" t="n"/>
+      <c r="AD104" s="11" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="11" t="n"/>
+      <c r="AG104" s="11" t="n"/>
+      <c r="AH104" s="11" t="n"/>
+      <c r="AI104" s="11" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="11" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -4064,6 +5417,18 @@
       <c r="W105" s="11" t="n"/>
       <c r="X105" s="11" t="n"/>
       <c r="Y105" s="11" t="n"/>
+      <c r="Z105" s="11" t="n"/>
+      <c r="AA105" s="11" t="n"/>
+      <c r="AB105" s="11" t="n"/>
+      <c r="AC105" s="11" t="n"/>
+      <c r="AD105" s="11" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="11" t="n"/>
+      <c r="AG105" s="11" t="n"/>
+      <c r="AH105" s="11" t="n"/>
+      <c r="AI105" s="11" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="11" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -4095,6 +5460,18 @@
       <c r="W106" s="11" t="n"/>
       <c r="X106" s="11" t="n"/>
       <c r="Y106" s="11" t="n"/>
+      <c r="Z106" s="11" t="n"/>
+      <c r="AA106" s="11" t="n"/>
+      <c r="AB106" s="11" t="n"/>
+      <c r="AC106" s="11" t="n"/>
+      <c r="AD106" s="11" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="11" t="n"/>
+      <c r="AG106" s="11" t="n"/>
+      <c r="AH106" s="11" t="n"/>
+      <c r="AI106" s="11" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="11" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -4126,6 +5503,18 @@
       <c r="W107" s="11" t="n"/>
       <c r="X107" s="11" t="n"/>
       <c r="Y107" s="11" t="n"/>
+      <c r="Z107" s="11" t="n"/>
+      <c r="AA107" s="11" t="n"/>
+      <c r="AB107" s="11" t="n"/>
+      <c r="AC107" s="11" t="n"/>
+      <c r="AD107" s="11" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="11" t="n"/>
+      <c r="AG107" s="11" t="n"/>
+      <c r="AH107" s="11" t="n"/>
+      <c r="AI107" s="11" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="11" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -4157,6 +5546,18 @@
       <c r="W108" s="11" t="n"/>
       <c r="X108" s="11" t="n"/>
       <c r="Y108" s="11" t="n"/>
+      <c r="Z108" s="11" t="n"/>
+      <c r="AA108" s="11" t="n"/>
+      <c r="AB108" s="11" t="n"/>
+      <c r="AC108" s="11" t="n"/>
+      <c r="AD108" s="11" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="11" t="n"/>
+      <c r="AG108" s="11" t="n"/>
+      <c r="AH108" s="11" t="n"/>
+      <c r="AI108" s="11" t="n"/>
+      <c r="AJ108" s="11" t="n"/>
+      <c r="AK108" s="11" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -4188,6 +5589,18 @@
       <c r="W109" s="11" t="n"/>
       <c r="X109" s="11" t="n"/>
       <c r="Y109" s="11" t="n"/>
+      <c r="Z109" s="11" t="n"/>
+      <c r="AA109" s="11" t="n"/>
+      <c r="AB109" s="11" t="n"/>
+      <c r="AC109" s="11" t="n"/>
+      <c r="AD109" s="11" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="11" t="n"/>
+      <c r="AG109" s="11" t="n"/>
+      <c r="AH109" s="11" t="n"/>
+      <c r="AI109" s="11" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="11" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -4219,6 +5632,18 @@
       <c r="W110" s="11" t="n"/>
       <c r="X110" s="11" t="n"/>
       <c r="Y110" s="11" t="n"/>
+      <c r="Z110" s="11" t="n"/>
+      <c r="AA110" s="11" t="n"/>
+      <c r="AB110" s="11" t="n"/>
+      <c r="AC110" s="11" t="n"/>
+      <c r="AD110" s="11" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="11" t="n"/>
+      <c r="AG110" s="11" t="n"/>
+      <c r="AH110" s="11" t="n"/>
+      <c r="AI110" s="11" t="n"/>
+      <c r="AJ110" s="11" t="n"/>
+      <c r="AK110" s="11" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -4250,6 +5675,18 @@
       <c r="W111" s="11" t="n"/>
       <c r="X111" s="11" t="n"/>
       <c r="Y111" s="11" t="n"/>
+      <c r="Z111" s="11" t="n"/>
+      <c r="AA111" s="11" t="n"/>
+      <c r="AB111" s="11" t="n"/>
+      <c r="AC111" s="11" t="n"/>
+      <c r="AD111" s="11" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="11" t="n"/>
+      <c r="AG111" s="11" t="n"/>
+      <c r="AH111" s="11" t="n"/>
+      <c r="AI111" s="11" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="11" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -4281,6 +5718,18 @@
       <c r="W112" s="11" t="n"/>
       <c r="X112" s="11" t="n"/>
       <c r="Y112" s="11" t="n"/>
+      <c r="Z112" s="11" t="n"/>
+      <c r="AA112" s="11" t="n"/>
+      <c r="AB112" s="11" t="n"/>
+      <c r="AC112" s="11" t="n"/>
+      <c r="AD112" s="11" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="11" t="n"/>
+      <c r="AG112" s="11" t="n"/>
+      <c r="AH112" s="11" t="n"/>
+      <c r="AI112" s="11" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="11" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -4312,6 +5761,18 @@
       <c r="W113" s="11" t="n"/>
       <c r="X113" s="11" t="n"/>
       <c r="Y113" s="11" t="n"/>
+      <c r="Z113" s="11" t="n"/>
+      <c r="AA113" s="11" t="n"/>
+      <c r="AB113" s="11" t="n"/>
+      <c r="AC113" s="11" t="n"/>
+      <c r="AD113" s="11" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="11" t="n"/>
+      <c r="AG113" s="11" t="n"/>
+      <c r="AH113" s="11" t="n"/>
+      <c r="AI113" s="11" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="11" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -4343,6 +5804,18 @@
       <c r="W114" s="11" t="n"/>
       <c r="X114" s="11" t="n"/>
       <c r="Y114" s="11" t="n"/>
+      <c r="Z114" s="11" t="n"/>
+      <c r="AA114" s="11" t="n"/>
+      <c r="AB114" s="11" t="n"/>
+      <c r="AC114" s="11" t="n"/>
+      <c r="AD114" s="11" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="11" t="n"/>
+      <c r="AG114" s="11" t="n"/>
+      <c r="AH114" s="11" t="n"/>
+      <c r="AI114" s="11" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="11" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -4374,6 +5847,18 @@
       <c r="W115" s="11" t="n"/>
       <c r="X115" s="11" t="n"/>
       <c r="Y115" s="11" t="n"/>
+      <c r="Z115" s="11" t="n"/>
+      <c r="AA115" s="11" t="n"/>
+      <c r="AB115" s="11" t="n"/>
+      <c r="AC115" s="11" t="n"/>
+      <c r="AD115" s="11" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="11" t="n"/>
+      <c r="AG115" s="11" t="n"/>
+      <c r="AH115" s="11" t="n"/>
+      <c r="AI115" s="11" t="n"/>
+      <c r="AJ115" s="11" t="n"/>
+      <c r="AK115" s="11" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -4405,6 +5890,18 @@
       <c r="W116" s="11" t="n"/>
       <c r="X116" s="11" t="n"/>
       <c r="Y116" s="11" t="n"/>
+      <c r="Z116" s="11" t="n"/>
+      <c r="AA116" s="11" t="n"/>
+      <c r="AB116" s="11" t="n"/>
+      <c r="AC116" s="11" t="n"/>
+      <c r="AD116" s="11" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="11" t="n"/>
+      <c r="AG116" s="11" t="n"/>
+      <c r="AH116" s="11" t="n"/>
+      <c r="AI116" s="11" t="n"/>
+      <c r="AJ116" s="11" t="n"/>
+      <c r="AK116" s="11" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -4436,6 +5933,18 @@
       <c r="W117" s="11" t="n"/>
       <c r="X117" s="11" t="n"/>
       <c r="Y117" s="11" t="n"/>
+      <c r="Z117" s="11" t="n"/>
+      <c r="AA117" s="11" t="n"/>
+      <c r="AB117" s="11" t="n"/>
+      <c r="AC117" s="11" t="n"/>
+      <c r="AD117" s="11" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="11" t="n"/>
+      <c r="AG117" s="11" t="n"/>
+      <c r="AH117" s="11" t="n"/>
+      <c r="AI117" s="11" t="n"/>
+      <c r="AJ117" s="11" t="n"/>
+      <c r="AK117" s="11" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -4467,6 +5976,18 @@
       <c r="W118" s="11" t="n"/>
       <c r="X118" s="11" t="n"/>
       <c r="Y118" s="11" t="n"/>
+      <c r="Z118" s="11" t="n"/>
+      <c r="AA118" s="11" t="n"/>
+      <c r="AB118" s="11" t="n"/>
+      <c r="AC118" s="11" t="n"/>
+      <c r="AD118" s="11" t="n"/>
+      <c r="AE118" s="11" t="n"/>
+      <c r="AF118" s="11" t="n"/>
+      <c r="AG118" s="11" t="n"/>
+      <c r="AH118" s="11" t="n"/>
+      <c r="AI118" s="11" t="n"/>
+      <c r="AJ118" s="11" t="n"/>
+      <c r="AK118" s="11" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -4498,6 +6019,18 @@
       <c r="W119" s="11" t="n"/>
       <c r="X119" s="11" t="n"/>
       <c r="Y119" s="11" t="n"/>
+      <c r="Z119" s="11" t="n"/>
+      <c r="AA119" s="11" t="n"/>
+      <c r="AB119" s="11" t="n"/>
+      <c r="AC119" s="11" t="n"/>
+      <c r="AD119" s="11" t="n"/>
+      <c r="AE119" s="11" t="n"/>
+      <c r="AF119" s="11" t="n"/>
+      <c r="AG119" s="11" t="n"/>
+      <c r="AH119" s="11" t="n"/>
+      <c r="AI119" s="11" t="n"/>
+      <c r="AJ119" s="11" t="n"/>
+      <c r="AK119" s="11" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -4529,6 +6062,18 @@
       <c r="W120" s="11" t="n"/>
       <c r="X120" s="11" t="n"/>
       <c r="Y120" s="11" t="n"/>
+      <c r="Z120" s="11" t="n"/>
+      <c r="AA120" s="11" t="n"/>
+      <c r="AB120" s="11" t="n"/>
+      <c r="AC120" s="11" t="n"/>
+      <c r="AD120" s="11" t="n"/>
+      <c r="AE120" s="11" t="n"/>
+      <c r="AF120" s="11" t="n"/>
+      <c r="AG120" s="11" t="n"/>
+      <c r="AH120" s="11" t="n"/>
+      <c r="AI120" s="11" t="n"/>
+      <c r="AJ120" s="11" t="n"/>
+      <c r="AK120" s="11" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -4560,6 +6105,18 @@
       <c r="W121" s="11" t="n"/>
       <c r="X121" s="11" t="n"/>
       <c r="Y121" s="11" t="n"/>
+      <c r="Z121" s="11" t="n"/>
+      <c r="AA121" s="11" t="n"/>
+      <c r="AB121" s="11" t="n"/>
+      <c r="AC121" s="11" t="n"/>
+      <c r="AD121" s="11" t="n"/>
+      <c r="AE121" s="11" t="n"/>
+      <c r="AF121" s="11" t="n"/>
+      <c r="AG121" s="11" t="n"/>
+      <c r="AH121" s="11" t="n"/>
+      <c r="AI121" s="11" t="n"/>
+      <c r="AJ121" s="11" t="n"/>
+      <c r="AK121" s="11" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -4591,6 +6148,18 @@
       <c r="W122" s="11" t="n"/>
       <c r="X122" s="11" t="n"/>
       <c r="Y122" s="11" t="n"/>
+      <c r="Z122" s="11" t="n"/>
+      <c r="AA122" s="11" t="n"/>
+      <c r="AB122" s="11" t="n"/>
+      <c r="AC122" s="11" t="n"/>
+      <c r="AD122" s="11" t="n"/>
+      <c r="AE122" s="11" t="n"/>
+      <c r="AF122" s="11" t="n"/>
+      <c r="AG122" s="11" t="n"/>
+      <c r="AH122" s="11" t="n"/>
+      <c r="AI122" s="11" t="n"/>
+      <c r="AJ122" s="11" t="n"/>
+      <c r="AK122" s="11" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -4622,6 +6191,18 @@
       <c r="W123" s="11" t="n"/>
       <c r="X123" s="11" t="n"/>
       <c r="Y123" s="11" t="n"/>
+      <c r="Z123" s="11" t="n"/>
+      <c r="AA123" s="11" t="n"/>
+      <c r="AB123" s="11" t="n"/>
+      <c r="AC123" s="11" t="n"/>
+      <c r="AD123" s="11" t="n"/>
+      <c r="AE123" s="11" t="n"/>
+      <c r="AF123" s="11" t="n"/>
+      <c r="AG123" s="11" t="n"/>
+      <c r="AH123" s="11" t="n"/>
+      <c r="AI123" s="11" t="n"/>
+      <c r="AJ123" s="11" t="n"/>
+      <c r="AK123" s="11" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -4653,6 +6234,18 @@
       <c r="W124" s="11" t="n"/>
       <c r="X124" s="11" t="n"/>
       <c r="Y124" s="11" t="n"/>
+      <c r="Z124" s="11" t="n"/>
+      <c r="AA124" s="11" t="n"/>
+      <c r="AB124" s="11" t="n"/>
+      <c r="AC124" s="11" t="n"/>
+      <c r="AD124" s="11" t="n"/>
+      <c r="AE124" s="11" t="n"/>
+      <c r="AF124" s="11" t="n"/>
+      <c r="AG124" s="11" t="n"/>
+      <c r="AH124" s="11" t="n"/>
+      <c r="AI124" s="11" t="n"/>
+      <c r="AJ124" s="11" t="n"/>
+      <c r="AK124" s="11" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -4684,6 +6277,18 @@
       <c r="W125" s="11" t="n"/>
       <c r="X125" s="11" t="n"/>
       <c r="Y125" s="11" t="n"/>
+      <c r="Z125" s="11" t="n"/>
+      <c r="AA125" s="11" t="n"/>
+      <c r="AB125" s="11" t="n"/>
+      <c r="AC125" s="11" t="n"/>
+      <c r="AD125" s="11" t="n"/>
+      <c r="AE125" s="11" t="n"/>
+      <c r="AF125" s="11" t="n"/>
+      <c r="AG125" s="11" t="n"/>
+      <c r="AH125" s="11" t="n"/>
+      <c r="AI125" s="11" t="n"/>
+      <c r="AJ125" s="11" t="n"/>
+      <c r="AK125" s="11" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -4715,6 +6320,18 @@
       <c r="W126" s="11" t="n"/>
       <c r="X126" s="11" t="n"/>
       <c r="Y126" s="11" t="n"/>
+      <c r="Z126" s="11" t="n"/>
+      <c r="AA126" s="11" t="n"/>
+      <c r="AB126" s="11" t="n"/>
+      <c r="AC126" s="11" t="n"/>
+      <c r="AD126" s="11" t="n"/>
+      <c r="AE126" s="11" t="n"/>
+      <c r="AF126" s="11" t="n"/>
+      <c r="AG126" s="11" t="n"/>
+      <c r="AH126" s="11" t="n"/>
+      <c r="AI126" s="11" t="n"/>
+      <c r="AJ126" s="11" t="n"/>
+      <c r="AK126" s="11" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -4746,6 +6363,18 @@
       <c r="W127" s="11" t="n"/>
       <c r="X127" s="11" t="n"/>
       <c r="Y127" s="11" t="n"/>
+      <c r="Z127" s="11" t="n"/>
+      <c r="AA127" s="11" t="n"/>
+      <c r="AB127" s="11" t="n"/>
+      <c r="AC127" s="11" t="n"/>
+      <c r="AD127" s="11" t="n"/>
+      <c r="AE127" s="11" t="n"/>
+      <c r="AF127" s="11" t="n"/>
+      <c r="AG127" s="11" t="n"/>
+      <c r="AH127" s="11" t="n"/>
+      <c r="AI127" s="11" t="n"/>
+      <c r="AJ127" s="11" t="n"/>
+      <c r="AK127" s="11" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -4777,6 +6406,18 @@
       <c r="W128" s="11" t="n"/>
       <c r="X128" s="11" t="n"/>
       <c r="Y128" s="11" t="n"/>
+      <c r="Z128" s="11" t="n"/>
+      <c r="AA128" s="11" t="n"/>
+      <c r="AB128" s="11" t="n"/>
+      <c r="AC128" s="11" t="n"/>
+      <c r="AD128" s="11" t="n"/>
+      <c r="AE128" s="11" t="n"/>
+      <c r="AF128" s="11" t="n"/>
+      <c r="AG128" s="11" t="n"/>
+      <c r="AH128" s="11" t="n"/>
+      <c r="AI128" s="11" t="n"/>
+      <c r="AJ128" s="11" t="n"/>
+      <c r="AK128" s="11" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -4808,6 +6449,18 @@
       <c r="W129" s="11" t="n"/>
       <c r="X129" s="11" t="n"/>
       <c r="Y129" s="11" t="n"/>
+      <c r="Z129" s="11" t="n"/>
+      <c r="AA129" s="11" t="n"/>
+      <c r="AB129" s="11" t="n"/>
+      <c r="AC129" s="11" t="n"/>
+      <c r="AD129" s="11" t="n"/>
+      <c r="AE129" s="11" t="n"/>
+      <c r="AF129" s="11" t="n"/>
+      <c r="AG129" s="11" t="n"/>
+      <c r="AH129" s="11" t="n"/>
+      <c r="AI129" s="11" t="n"/>
+      <c r="AJ129" s="11" t="n"/>
+      <c r="AK129" s="11" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -4839,6 +6492,18 @@
       <c r="W130" s="11" t="n"/>
       <c r="X130" s="11" t="n"/>
       <c r="Y130" s="11" t="n"/>
+      <c r="Z130" s="11" t="n"/>
+      <c r="AA130" s="11" t="n"/>
+      <c r="AB130" s="11" t="n"/>
+      <c r="AC130" s="11" t="n"/>
+      <c r="AD130" s="11" t="n"/>
+      <c r="AE130" s="11" t="n"/>
+      <c r="AF130" s="11" t="n"/>
+      <c r="AG130" s="11" t="n"/>
+      <c r="AH130" s="11" t="n"/>
+      <c r="AI130" s="11" t="n"/>
+      <c r="AJ130" s="11" t="n"/>
+      <c r="AK130" s="11" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -4870,6 +6535,18 @@
       <c r="W131" s="11" t="n"/>
       <c r="X131" s="11" t="n"/>
       <c r="Y131" s="11" t="n"/>
+      <c r="Z131" s="11" t="n"/>
+      <c r="AA131" s="11" t="n"/>
+      <c r="AB131" s="11" t="n"/>
+      <c r="AC131" s="11" t="n"/>
+      <c r="AD131" s="11" t="n"/>
+      <c r="AE131" s="11" t="n"/>
+      <c r="AF131" s="11" t="n"/>
+      <c r="AG131" s="11" t="n"/>
+      <c r="AH131" s="11" t="n"/>
+      <c r="AI131" s="11" t="n"/>
+      <c r="AJ131" s="11" t="n"/>
+      <c r="AK131" s="11" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -4901,6 +6578,18 @@
       <c r="W132" s="11" t="n"/>
       <c r="X132" s="11" t="n"/>
       <c r="Y132" s="11" t="n"/>
+      <c r="Z132" s="11" t="n"/>
+      <c r="AA132" s="11" t="n"/>
+      <c r="AB132" s="11" t="n"/>
+      <c r="AC132" s="11" t="n"/>
+      <c r="AD132" s="11" t="n"/>
+      <c r="AE132" s="11" t="n"/>
+      <c r="AF132" s="11" t="n"/>
+      <c r="AG132" s="11" t="n"/>
+      <c r="AH132" s="11" t="n"/>
+      <c r="AI132" s="11" t="n"/>
+      <c r="AJ132" s="11" t="n"/>
+      <c r="AK132" s="11" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -4932,6 +6621,18 @@
       <c r="W133" s="11" t="n"/>
       <c r="X133" s="11" t="n"/>
       <c r="Y133" s="11" t="n"/>
+      <c r="Z133" s="11" t="n"/>
+      <c r="AA133" s="11" t="n"/>
+      <c r="AB133" s="11" t="n"/>
+      <c r="AC133" s="11" t="n"/>
+      <c r="AD133" s="11" t="n"/>
+      <c r="AE133" s="11" t="n"/>
+      <c r="AF133" s="11" t="n"/>
+      <c r="AG133" s="11" t="n"/>
+      <c r="AH133" s="11" t="n"/>
+      <c r="AI133" s="11" t="n"/>
+      <c r="AJ133" s="11" t="n"/>
+      <c r="AK133" s="11" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -4963,6 +6664,18 @@
       <c r="W134" s="11" t="n"/>
       <c r="X134" s="11" t="n"/>
       <c r="Y134" s="11" t="n"/>
+      <c r="Z134" s="11" t="n"/>
+      <c r="AA134" s="11" t="n"/>
+      <c r="AB134" s="11" t="n"/>
+      <c r="AC134" s="11" t="n"/>
+      <c r="AD134" s="11" t="n"/>
+      <c r="AE134" s="11" t="n"/>
+      <c r="AF134" s="11" t="n"/>
+      <c r="AG134" s="11" t="n"/>
+      <c r="AH134" s="11" t="n"/>
+      <c r="AI134" s="11" t="n"/>
+      <c r="AJ134" s="11" t="n"/>
+      <c r="AK134" s="11" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -4994,6 +6707,18 @@
       <c r="W135" s="11" t="n"/>
       <c r="X135" s="11" t="n"/>
       <c r="Y135" s="11" t="n"/>
+      <c r="Z135" s="11" t="n"/>
+      <c r="AA135" s="11" t="n"/>
+      <c r="AB135" s="11" t="n"/>
+      <c r="AC135" s="11" t="n"/>
+      <c r="AD135" s="11" t="n"/>
+      <c r="AE135" s="11" t="n"/>
+      <c r="AF135" s="11" t="n"/>
+      <c r="AG135" s="11" t="n"/>
+      <c r="AH135" s="11" t="n"/>
+      <c r="AI135" s="11" t="n"/>
+      <c r="AJ135" s="11" t="n"/>
+      <c r="AK135" s="11" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -5025,6 +6750,18 @@
       <c r="W136" s="11" t="n"/>
       <c r="X136" s="11" t="n"/>
       <c r="Y136" s="11" t="n"/>
+      <c r="Z136" s="11" t="n"/>
+      <c r="AA136" s="11" t="n"/>
+      <c r="AB136" s="11" t="n"/>
+      <c r="AC136" s="11" t="n"/>
+      <c r="AD136" s="11" t="n"/>
+      <c r="AE136" s="11" t="n"/>
+      <c r="AF136" s="11" t="n"/>
+      <c r="AG136" s="11" t="n"/>
+      <c r="AH136" s="11" t="n"/>
+      <c r="AI136" s="11" t="n"/>
+      <c r="AJ136" s="11" t="n"/>
+      <c r="AK136" s="11" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -5056,6 +6793,18 @@
       <c r="W137" s="11" t="n"/>
       <c r="X137" s="11" t="n"/>
       <c r="Y137" s="11" t="n"/>
+      <c r="Z137" s="11" t="n"/>
+      <c r="AA137" s="11" t="n"/>
+      <c r="AB137" s="11" t="n"/>
+      <c r="AC137" s="11" t="n"/>
+      <c r="AD137" s="11" t="n"/>
+      <c r="AE137" s="11" t="n"/>
+      <c r="AF137" s="11" t="n"/>
+      <c r="AG137" s="11" t="n"/>
+      <c r="AH137" s="11" t="n"/>
+      <c r="AI137" s="11" t="n"/>
+      <c r="AJ137" s="11" t="n"/>
+      <c r="AK137" s="11" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -5087,6 +6836,18 @@
       <c r="W138" s="11" t="n"/>
       <c r="X138" s="11" t="n"/>
       <c r="Y138" s="11" t="n"/>
+      <c r="Z138" s="11" t="n"/>
+      <c r="AA138" s="11" t="n"/>
+      <c r="AB138" s="11" t="n"/>
+      <c r="AC138" s="11" t="n"/>
+      <c r="AD138" s="11" t="n"/>
+      <c r="AE138" s="11" t="n"/>
+      <c r="AF138" s="11" t="n"/>
+      <c r="AG138" s="11" t="n"/>
+      <c r="AH138" s="11" t="n"/>
+      <c r="AI138" s="11" t="n"/>
+      <c r="AJ138" s="11" t="n"/>
+      <c r="AK138" s="11" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -5118,6 +6879,18 @@
       <c r="W139" s="11" t="n"/>
       <c r="X139" s="11" t="n"/>
       <c r="Y139" s="11" t="n"/>
+      <c r="Z139" s="11" t="n"/>
+      <c r="AA139" s="11" t="n"/>
+      <c r="AB139" s="11" t="n"/>
+      <c r="AC139" s="11" t="n"/>
+      <c r="AD139" s="11" t="n"/>
+      <c r="AE139" s="11" t="n"/>
+      <c r="AF139" s="11" t="n"/>
+      <c r="AG139" s="11" t="n"/>
+      <c r="AH139" s="11" t="n"/>
+      <c r="AI139" s="11" t="n"/>
+      <c r="AJ139" s="11" t="n"/>
+      <c r="AK139" s="11" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -5149,6 +6922,18 @@
       <c r="W140" s="11" t="n"/>
       <c r="X140" s="11" t="n"/>
       <c r="Y140" s="11" t="n"/>
+      <c r="Z140" s="11" t="n"/>
+      <c r="AA140" s="11" t="n"/>
+      <c r="AB140" s="11" t="n"/>
+      <c r="AC140" s="11" t="n"/>
+      <c r="AD140" s="11" t="n"/>
+      <c r="AE140" s="11" t="n"/>
+      <c r="AF140" s="11" t="n"/>
+      <c r="AG140" s="11" t="n"/>
+      <c r="AH140" s="11" t="n"/>
+      <c r="AI140" s="11" t="n"/>
+      <c r="AJ140" s="11" t="n"/>
+      <c r="AK140" s="11" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -5180,6 +6965,18 @@
       <c r="W141" s="11" t="n"/>
       <c r="X141" s="11" t="n"/>
       <c r="Y141" s="11" t="n"/>
+      <c r="Z141" s="11" t="n"/>
+      <c r="AA141" s="11" t="n"/>
+      <c r="AB141" s="11" t="n"/>
+      <c r="AC141" s="11" t="n"/>
+      <c r="AD141" s="11" t="n"/>
+      <c r="AE141" s="11" t="n"/>
+      <c r="AF141" s="11" t="n"/>
+      <c r="AG141" s="11" t="n"/>
+      <c r="AH141" s="11" t="n"/>
+      <c r="AI141" s="11" t="n"/>
+      <c r="AJ141" s="11" t="n"/>
+      <c r="AK141" s="11" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -5211,6 +7008,18 @@
       <c r="W142" s="11" t="n"/>
       <c r="X142" s="11" t="n"/>
       <c r="Y142" s="11" t="n"/>
+      <c r="Z142" s="11" t="n"/>
+      <c r="AA142" s="11" t="n"/>
+      <c r="AB142" s="11" t="n"/>
+      <c r="AC142" s="11" t="n"/>
+      <c r="AD142" s="11" t="n"/>
+      <c r="AE142" s="11" t="n"/>
+      <c r="AF142" s="11" t="n"/>
+      <c r="AG142" s="11" t="n"/>
+      <c r="AH142" s="11" t="n"/>
+      <c r="AI142" s="11" t="n"/>
+      <c r="AJ142" s="11" t="n"/>
+      <c r="AK142" s="11" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -5242,6 +7051,18 @@
       <c r="W143" s="11" t="n"/>
       <c r="X143" s="11" t="n"/>
       <c r="Y143" s="11" t="n"/>
+      <c r="Z143" s="11" t="n"/>
+      <c r="AA143" s="11" t="n"/>
+      <c r="AB143" s="11" t="n"/>
+      <c r="AC143" s="11" t="n"/>
+      <c r="AD143" s="11" t="n"/>
+      <c r="AE143" s="11" t="n"/>
+      <c r="AF143" s="11" t="n"/>
+      <c r="AG143" s="11" t="n"/>
+      <c r="AH143" s="11" t="n"/>
+      <c r="AI143" s="11" t="n"/>
+      <c r="AJ143" s="11" t="n"/>
+      <c r="AK143" s="11" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -5273,6 +7094,18 @@
       <c r="W144" s="11" t="n"/>
       <c r="X144" s="11" t="n"/>
       <c r="Y144" s="11" t="n"/>
+      <c r="Z144" s="11" t="n"/>
+      <c r="AA144" s="11" t="n"/>
+      <c r="AB144" s="11" t="n"/>
+      <c r="AC144" s="11" t="n"/>
+      <c r="AD144" s="11" t="n"/>
+      <c r="AE144" s="11" t="n"/>
+      <c r="AF144" s="11" t="n"/>
+      <c r="AG144" s="11" t="n"/>
+      <c r="AH144" s="11" t="n"/>
+      <c r="AI144" s="11" t="n"/>
+      <c r="AJ144" s="11" t="n"/>
+      <c r="AK144" s="11" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -5304,6 +7137,18 @@
       <c r="W145" s="11" t="n"/>
       <c r="X145" s="11" t="n"/>
       <c r="Y145" s="11" t="n"/>
+      <c r="Z145" s="11" t="n"/>
+      <c r="AA145" s="11" t="n"/>
+      <c r="AB145" s="11" t="n"/>
+      <c r="AC145" s="11" t="n"/>
+      <c r="AD145" s="11" t="n"/>
+      <c r="AE145" s="11" t="n"/>
+      <c r="AF145" s="11" t="n"/>
+      <c r="AG145" s="11" t="n"/>
+      <c r="AH145" s="11" t="n"/>
+      <c r="AI145" s="11" t="n"/>
+      <c r="AJ145" s="11" t="n"/>
+      <c r="AK145" s="11" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -5335,6 +7180,18 @@
       <c r="W146" s="11" t="n"/>
       <c r="X146" s="11" t="n"/>
       <c r="Y146" s="11" t="n"/>
+      <c r="Z146" s="11" t="n"/>
+      <c r="AA146" s="11" t="n"/>
+      <c r="AB146" s="11" t="n"/>
+      <c r="AC146" s="11" t="n"/>
+      <c r="AD146" s="11" t="n"/>
+      <c r="AE146" s="11" t="n"/>
+      <c r="AF146" s="11" t="n"/>
+      <c r="AG146" s="11" t="n"/>
+      <c r="AH146" s="11" t="n"/>
+      <c r="AI146" s="11" t="n"/>
+      <c r="AJ146" s="11" t="n"/>
+      <c r="AK146" s="11" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -5366,6 +7223,18 @@
       <c r="W147" s="11" t="n"/>
       <c r="X147" s="11" t="n"/>
       <c r="Y147" s="11" t="n"/>
+      <c r="Z147" s="11" t="n"/>
+      <c r="AA147" s="11" t="n"/>
+      <c r="AB147" s="11" t="n"/>
+      <c r="AC147" s="11" t="n"/>
+      <c r="AD147" s="11" t="n"/>
+      <c r="AE147" s="11" t="n"/>
+      <c r="AF147" s="11" t="n"/>
+      <c r="AG147" s="11" t="n"/>
+      <c r="AH147" s="11" t="n"/>
+      <c r="AI147" s="11" t="n"/>
+      <c r="AJ147" s="11" t="n"/>
+      <c r="AK147" s="11" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -5397,6 +7266,18 @@
       <c r="W148" s="11" t="n"/>
       <c r="X148" s="11" t="n"/>
       <c r="Y148" s="11" t="n"/>
+      <c r="Z148" s="11" t="n"/>
+      <c r="AA148" s="11" t="n"/>
+      <c r="AB148" s="11" t="n"/>
+      <c r="AC148" s="11" t="n"/>
+      <c r="AD148" s="11" t="n"/>
+      <c r="AE148" s="11" t="n"/>
+      <c r="AF148" s="11" t="n"/>
+      <c r="AG148" s="11" t="n"/>
+      <c r="AH148" s="11" t="n"/>
+      <c r="AI148" s="11" t="n"/>
+      <c r="AJ148" s="11" t="n"/>
+      <c r="AK148" s="11" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -5428,6 +7309,18 @@
       <c r="W149" s="11" t="n"/>
       <c r="X149" s="11" t="n"/>
       <c r="Y149" s="11" t="n"/>
+      <c r="Z149" s="11" t="n"/>
+      <c r="AA149" s="11" t="n"/>
+      <c r="AB149" s="11" t="n"/>
+      <c r="AC149" s="11" t="n"/>
+      <c r="AD149" s="11" t="n"/>
+      <c r="AE149" s="11" t="n"/>
+      <c r="AF149" s="11" t="n"/>
+      <c r="AG149" s="11" t="n"/>
+      <c r="AH149" s="11" t="n"/>
+      <c r="AI149" s="11" t="n"/>
+      <c r="AJ149" s="11" t="n"/>
+      <c r="AK149" s="11" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -5459,6 +7352,18 @@
       <c r="W150" s="11" t="n"/>
       <c r="X150" s="11" t="n"/>
       <c r="Y150" s="11" t="n"/>
+      <c r="Z150" s="11" t="n"/>
+      <c r="AA150" s="11" t="n"/>
+      <c r="AB150" s="11" t="n"/>
+      <c r="AC150" s="11" t="n"/>
+      <c r="AD150" s="11" t="n"/>
+      <c r="AE150" s="11" t="n"/>
+      <c r="AF150" s="11" t="n"/>
+      <c r="AG150" s="11" t="n"/>
+      <c r="AH150" s="11" t="n"/>
+      <c r="AI150" s="11" t="n"/>
+      <c r="AJ150" s="11" t="n"/>
+      <c r="AK150" s="11" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -5490,6 +7395,18 @@
       <c r="W151" s="11" t="n"/>
       <c r="X151" s="11" t="n"/>
       <c r="Y151" s="11" t="n"/>
+      <c r="Z151" s="11" t="n"/>
+      <c r="AA151" s="11" t="n"/>
+      <c r="AB151" s="11" t="n"/>
+      <c r="AC151" s="11" t="n"/>
+      <c r="AD151" s="11" t="n"/>
+      <c r="AE151" s="11" t="n"/>
+      <c r="AF151" s="11" t="n"/>
+      <c r="AG151" s="11" t="n"/>
+      <c r="AH151" s="11" t="n"/>
+      <c r="AI151" s="11" t="n"/>
+      <c r="AJ151" s="11" t="n"/>
+      <c r="AK151" s="11" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -5521,6 +7438,18 @@
       <c r="W152" s="11" t="n"/>
       <c r="X152" s="11" t="n"/>
       <c r="Y152" s="11" t="n"/>
+      <c r="Z152" s="11" t="n"/>
+      <c r="AA152" s="11" t="n"/>
+      <c r="AB152" s="11" t="n"/>
+      <c r="AC152" s="11" t="n"/>
+      <c r="AD152" s="11" t="n"/>
+      <c r="AE152" s="11" t="n"/>
+      <c r="AF152" s="11" t="n"/>
+      <c r="AG152" s="11" t="n"/>
+      <c r="AH152" s="11" t="n"/>
+      <c r="AI152" s="11" t="n"/>
+      <c r="AJ152" s="11" t="n"/>
+      <c r="AK152" s="11" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -5552,6 +7481,18 @@
       <c r="W153" s="11" t="n"/>
       <c r="X153" s="11" t="n"/>
       <c r="Y153" s="11" t="n"/>
+      <c r="Z153" s="11" t="n"/>
+      <c r="AA153" s="11" t="n"/>
+      <c r="AB153" s="11" t="n"/>
+      <c r="AC153" s="11" t="n"/>
+      <c r="AD153" s="11" t="n"/>
+      <c r="AE153" s="11" t="n"/>
+      <c r="AF153" s="11" t="n"/>
+      <c r="AG153" s="11" t="n"/>
+      <c r="AH153" s="11" t="n"/>
+      <c r="AI153" s="11" t="n"/>
+      <c r="AJ153" s="11" t="n"/>
+      <c r="AK153" s="11" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -5583,6 +7524,18 @@
       <c r="W154" s="11" t="n"/>
       <c r="X154" s="11" t="n"/>
       <c r="Y154" s="11" t="n"/>
+      <c r="Z154" s="11" t="n"/>
+      <c r="AA154" s="11" t="n"/>
+      <c r="AB154" s="11" t="n"/>
+      <c r="AC154" s="11" t="n"/>
+      <c r="AD154" s="11" t="n"/>
+      <c r="AE154" s="11" t="n"/>
+      <c r="AF154" s="11" t="n"/>
+      <c r="AG154" s="11" t="n"/>
+      <c r="AH154" s="11" t="n"/>
+      <c r="AI154" s="11" t="n"/>
+      <c r="AJ154" s="11" t="n"/>
+      <c r="AK154" s="11" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -5614,6 +7567,18 @@
       <c r="W155" s="11" t="n"/>
       <c r="X155" s="11" t="n"/>
       <c r="Y155" s="11" t="n"/>
+      <c r="Z155" s="11" t="n"/>
+      <c r="AA155" s="11" t="n"/>
+      <c r="AB155" s="11" t="n"/>
+      <c r="AC155" s="11" t="n"/>
+      <c r="AD155" s="11" t="n"/>
+      <c r="AE155" s="11" t="n"/>
+      <c r="AF155" s="11" t="n"/>
+      <c r="AG155" s="11" t="n"/>
+      <c r="AH155" s="11" t="n"/>
+      <c r="AI155" s="11" t="n"/>
+      <c r="AJ155" s="11" t="n"/>
+      <c r="AK155" s="11" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -5645,6 +7610,18 @@
       <c r="W156" s="11" t="n"/>
       <c r="X156" s="11" t="n"/>
       <c r="Y156" s="11" t="n"/>
+      <c r="Z156" s="11" t="n"/>
+      <c r="AA156" s="11" t="n"/>
+      <c r="AB156" s="11" t="n"/>
+      <c r="AC156" s="11" t="n"/>
+      <c r="AD156" s="11" t="n"/>
+      <c r="AE156" s="11" t="n"/>
+      <c r="AF156" s="11" t="n"/>
+      <c r="AG156" s="11" t="n"/>
+      <c r="AH156" s="11" t="n"/>
+      <c r="AI156" s="11" t="n"/>
+      <c r="AJ156" s="11" t="n"/>
+      <c r="AK156" s="11" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -5676,6 +7653,18 @@
       <c r="W157" s="11" t="n"/>
       <c r="X157" s="11" t="n"/>
       <c r="Y157" s="11" t="n"/>
+      <c r="Z157" s="11" t="n"/>
+      <c r="AA157" s="11" t="n"/>
+      <c r="AB157" s="11" t="n"/>
+      <c r="AC157" s="11" t="n"/>
+      <c r="AD157" s="11" t="n"/>
+      <c r="AE157" s="11" t="n"/>
+      <c r="AF157" s="11" t="n"/>
+      <c r="AG157" s="11" t="n"/>
+      <c r="AH157" s="11" t="n"/>
+      <c r="AI157" s="11" t="n"/>
+      <c r="AJ157" s="11" t="n"/>
+      <c r="AK157" s="11" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -5707,6 +7696,18 @@
       <c r="W158" s="11" t="n"/>
       <c r="X158" s="11" t="n"/>
       <c r="Y158" s="11" t="n"/>
+      <c r="Z158" s="11" t="n"/>
+      <c r="AA158" s="11" t="n"/>
+      <c r="AB158" s="11" t="n"/>
+      <c r="AC158" s="11" t="n"/>
+      <c r="AD158" s="11" t="n"/>
+      <c r="AE158" s="11" t="n"/>
+      <c r="AF158" s="11" t="n"/>
+      <c r="AG158" s="11" t="n"/>
+      <c r="AH158" s="11" t="n"/>
+      <c r="AI158" s="11" t="n"/>
+      <c r="AJ158" s="11" t="n"/>
+      <c r="AK158" s="11" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -5738,6 +7739,18 @@
       <c r="W159" s="11" t="n"/>
       <c r="X159" s="11" t="n"/>
       <c r="Y159" s="11" t="n"/>
+      <c r="Z159" s="11" t="n"/>
+      <c r="AA159" s="11" t="n"/>
+      <c r="AB159" s="11" t="n"/>
+      <c r="AC159" s="11" t="n"/>
+      <c r="AD159" s="11" t="n"/>
+      <c r="AE159" s="11" t="n"/>
+      <c r="AF159" s="11" t="n"/>
+      <c r="AG159" s="11" t="n"/>
+      <c r="AH159" s="11" t="n"/>
+      <c r="AI159" s="11" t="n"/>
+      <c r="AJ159" s="11" t="n"/>
+      <c r="AK159" s="11" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -5769,6 +7782,18 @@
       <c r="W160" s="11" t="n"/>
       <c r="X160" s="11" t="n"/>
       <c r="Y160" s="11" t="n"/>
+      <c r="Z160" s="11" t="n"/>
+      <c r="AA160" s="11" t="n"/>
+      <c r="AB160" s="11" t="n"/>
+      <c r="AC160" s="11" t="n"/>
+      <c r="AD160" s="11" t="n"/>
+      <c r="AE160" s="11" t="n"/>
+      <c r="AF160" s="11" t="n"/>
+      <c r="AG160" s="11" t="n"/>
+      <c r="AH160" s="11" t="n"/>
+      <c r="AI160" s="11" t="n"/>
+      <c r="AJ160" s="11" t="n"/>
+      <c r="AK160" s="11" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -5800,6 +7825,18 @@
       <c r="W161" s="11" t="n"/>
       <c r="X161" s="11" t="n"/>
       <c r="Y161" s="11" t="n"/>
+      <c r="Z161" s="11" t="n"/>
+      <c r="AA161" s="11" t="n"/>
+      <c r="AB161" s="11" t="n"/>
+      <c r="AC161" s="11" t="n"/>
+      <c r="AD161" s="11" t="n"/>
+      <c r="AE161" s="11" t="n"/>
+      <c r="AF161" s="11" t="n"/>
+      <c r="AG161" s="11" t="n"/>
+      <c r="AH161" s="11" t="n"/>
+      <c r="AI161" s="11" t="n"/>
+      <c r="AJ161" s="11" t="n"/>
+      <c r="AK161" s="11" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -5831,6 +7868,18 @@
       <c r="W162" s="11" t="n"/>
       <c r="X162" s="11" t="n"/>
       <c r="Y162" s="11" t="n"/>
+      <c r="Z162" s="11" t="n"/>
+      <c r="AA162" s="11" t="n"/>
+      <c r="AB162" s="11" t="n"/>
+      <c r="AC162" s="11" t="n"/>
+      <c r="AD162" s="11" t="n"/>
+      <c r="AE162" s="11" t="n"/>
+      <c r="AF162" s="11" t="n"/>
+      <c r="AG162" s="11" t="n"/>
+      <c r="AH162" s="11" t="n"/>
+      <c r="AI162" s="11" t="n"/>
+      <c r="AJ162" s="11" t="n"/>
+      <c r="AK162" s="11" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -5862,6 +7911,18 @@
       <c r="W163" s="11" t="n"/>
       <c r="X163" s="11" t="n"/>
       <c r="Y163" s="11" t="n"/>
+      <c r="Z163" s="11" t="n"/>
+      <c r="AA163" s="11" t="n"/>
+      <c r="AB163" s="11" t="n"/>
+      <c r="AC163" s="11" t="n"/>
+      <c r="AD163" s="11" t="n"/>
+      <c r="AE163" s="11" t="n"/>
+      <c r="AF163" s="11" t="n"/>
+      <c r="AG163" s="11" t="n"/>
+      <c r="AH163" s="11" t="n"/>
+      <c r="AI163" s="11" t="n"/>
+      <c r="AJ163" s="11" t="n"/>
+      <c r="AK163" s="11" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -5893,6 +7954,18 @@
       <c r="W164" s="11" t="n"/>
       <c r="X164" s="11" t="n"/>
       <c r="Y164" s="11" t="n"/>
+      <c r="Z164" s="11" t="n"/>
+      <c r="AA164" s="11" t="n"/>
+      <c r="AB164" s="11" t="n"/>
+      <c r="AC164" s="11" t="n"/>
+      <c r="AD164" s="11" t="n"/>
+      <c r="AE164" s="11" t="n"/>
+      <c r="AF164" s="11" t="n"/>
+      <c r="AG164" s="11" t="n"/>
+      <c r="AH164" s="11" t="n"/>
+      <c r="AI164" s="11" t="n"/>
+      <c r="AJ164" s="11" t="n"/>
+      <c r="AK164" s="11" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -5924,6 +7997,18 @@
       <c r="W165" s="11" t="n"/>
       <c r="X165" s="11" t="n"/>
       <c r="Y165" s="11" t="n"/>
+      <c r="Z165" s="11" t="n"/>
+      <c r="AA165" s="11" t="n"/>
+      <c r="AB165" s="11" t="n"/>
+      <c r="AC165" s="11" t="n"/>
+      <c r="AD165" s="11" t="n"/>
+      <c r="AE165" s="11" t="n"/>
+      <c r="AF165" s="11" t="n"/>
+      <c r="AG165" s="11" t="n"/>
+      <c r="AH165" s="11" t="n"/>
+      <c r="AI165" s="11" t="n"/>
+      <c r="AJ165" s="11" t="n"/>
+      <c r="AK165" s="11" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -5955,6 +8040,18 @@
       <c r="W166" s="11" t="n"/>
       <c r="X166" s="11" t="n"/>
       <c r="Y166" s="11" t="n"/>
+      <c r="Z166" s="11" t="n"/>
+      <c r="AA166" s="11" t="n"/>
+      <c r="AB166" s="11" t="n"/>
+      <c r="AC166" s="11" t="n"/>
+      <c r="AD166" s="11" t="n"/>
+      <c r="AE166" s="11" t="n"/>
+      <c r="AF166" s="11" t="n"/>
+      <c r="AG166" s="11" t="n"/>
+      <c r="AH166" s="11" t="n"/>
+      <c r="AI166" s="11" t="n"/>
+      <c r="AJ166" s="11" t="n"/>
+      <c r="AK166" s="11" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -5986,6 +8083,18 @@
       <c r="W167" s="11" t="n"/>
       <c r="X167" s="11" t="n"/>
       <c r="Y167" s="11" t="n"/>
+      <c r="Z167" s="11" t="n"/>
+      <c r="AA167" s="11" t="n"/>
+      <c r="AB167" s="11" t="n"/>
+      <c r="AC167" s="11" t="n"/>
+      <c r="AD167" s="11" t="n"/>
+      <c r="AE167" s="11" t="n"/>
+      <c r="AF167" s="11" t="n"/>
+      <c r="AG167" s="11" t="n"/>
+      <c r="AH167" s="11" t="n"/>
+      <c r="AI167" s="11" t="n"/>
+      <c r="AJ167" s="11" t="n"/>
+      <c r="AK167" s="11" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -6017,6 +8126,18 @@
       <c r="W168" s="11" t="n"/>
       <c r="X168" s="11" t="n"/>
       <c r="Y168" s="11" t="n"/>
+      <c r="Z168" s="11" t="n"/>
+      <c r="AA168" s="11" t="n"/>
+      <c r="AB168" s="11" t="n"/>
+      <c r="AC168" s="11" t="n"/>
+      <c r="AD168" s="11" t="n"/>
+      <c r="AE168" s="11" t="n"/>
+      <c r="AF168" s="11" t="n"/>
+      <c r="AG168" s="11" t="n"/>
+      <c r="AH168" s="11" t="n"/>
+      <c r="AI168" s="11" t="n"/>
+      <c r="AJ168" s="11" t="n"/>
+      <c r="AK168" s="11" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -6048,6 +8169,18 @@
       <c r="W169" s="11" t="n"/>
       <c r="X169" s="11" t="n"/>
       <c r="Y169" s="11" t="n"/>
+      <c r="Z169" s="11" t="n"/>
+      <c r="AA169" s="11" t="n"/>
+      <c r="AB169" s="11" t="n"/>
+      <c r="AC169" s="11" t="n"/>
+      <c r="AD169" s="11" t="n"/>
+      <c r="AE169" s="11" t="n"/>
+      <c r="AF169" s="11" t="n"/>
+      <c r="AG169" s="11" t="n"/>
+      <c r="AH169" s="11" t="n"/>
+      <c r="AI169" s="11" t="n"/>
+      <c r="AJ169" s="11" t="n"/>
+      <c r="AK169" s="11" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -6079,6 +8212,18 @@
       <c r="W170" s="11" t="n"/>
       <c r="X170" s="11" t="n"/>
       <c r="Y170" s="11" t="n"/>
+      <c r="Z170" s="11" t="n"/>
+      <c r="AA170" s="11" t="n"/>
+      <c r="AB170" s="11" t="n"/>
+      <c r="AC170" s="11" t="n"/>
+      <c r="AD170" s="11" t="n"/>
+      <c r="AE170" s="11" t="n"/>
+      <c r="AF170" s="11" t="n"/>
+      <c r="AG170" s="11" t="n"/>
+      <c r="AH170" s="11" t="n"/>
+      <c r="AI170" s="11" t="n"/>
+      <c r="AJ170" s="11" t="n"/>
+      <c r="AK170" s="11" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -6110,6 +8255,18 @@
       <c r="W171" s="11" t="n"/>
       <c r="X171" s="11" t="n"/>
       <c r="Y171" s="11" t="n"/>
+      <c r="Z171" s="11" t="n"/>
+      <c r="AA171" s="11" t="n"/>
+      <c r="AB171" s="11" t="n"/>
+      <c r="AC171" s="11" t="n"/>
+      <c r="AD171" s="11" t="n"/>
+      <c r="AE171" s="11" t="n"/>
+      <c r="AF171" s="11" t="n"/>
+      <c r="AG171" s="11" t="n"/>
+      <c r="AH171" s="11" t="n"/>
+      <c r="AI171" s="11" t="n"/>
+      <c r="AJ171" s="11" t="n"/>
+      <c r="AK171" s="11" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -6141,6 +8298,18 @@
       <c r="W172" s="11" t="n"/>
       <c r="X172" s="11" t="n"/>
       <c r="Y172" s="11" t="n"/>
+      <c r="Z172" s="11" t="n"/>
+      <c r="AA172" s="11" t="n"/>
+      <c r="AB172" s="11" t="n"/>
+      <c r="AC172" s="11" t="n"/>
+      <c r="AD172" s="11" t="n"/>
+      <c r="AE172" s="11" t="n"/>
+      <c r="AF172" s="11" t="n"/>
+      <c r="AG172" s="11" t="n"/>
+      <c r="AH172" s="11" t="n"/>
+      <c r="AI172" s="11" t="n"/>
+      <c r="AJ172" s="11" t="n"/>
+      <c r="AK172" s="11" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -6172,6 +8341,18 @@
       <c r="W173" s="11" t="n"/>
       <c r="X173" s="11" t="n"/>
       <c r="Y173" s="11" t="n"/>
+      <c r="Z173" s="11" t="n"/>
+      <c r="AA173" s="11" t="n"/>
+      <c r="AB173" s="11" t="n"/>
+      <c r="AC173" s="11" t="n"/>
+      <c r="AD173" s="11" t="n"/>
+      <c r="AE173" s="11" t="n"/>
+      <c r="AF173" s="11" t="n"/>
+      <c r="AG173" s="11" t="n"/>
+      <c r="AH173" s="11" t="n"/>
+      <c r="AI173" s="11" t="n"/>
+      <c r="AJ173" s="11" t="n"/>
+      <c r="AK173" s="11" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -6203,6 +8384,18 @@
       <c r="W174" s="11" t="n"/>
       <c r="X174" s="11" t="n"/>
       <c r="Y174" s="11" t="n"/>
+      <c r="Z174" s="11" t="n"/>
+      <c r="AA174" s="11" t="n"/>
+      <c r="AB174" s="11" t="n"/>
+      <c r="AC174" s="11" t="n"/>
+      <c r="AD174" s="11" t="n"/>
+      <c r="AE174" s="11" t="n"/>
+      <c r="AF174" s="11" t="n"/>
+      <c r="AG174" s="11" t="n"/>
+      <c r="AH174" s="11" t="n"/>
+      <c r="AI174" s="11" t="n"/>
+      <c r="AJ174" s="11" t="n"/>
+      <c r="AK174" s="11" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -6234,6 +8427,18 @@
       <c r="W175" s="11" t="n"/>
       <c r="X175" s="11" t="n"/>
       <c r="Y175" s="11" t="n"/>
+      <c r="Z175" s="11" t="n"/>
+      <c r="AA175" s="11" t="n"/>
+      <c r="AB175" s="11" t="n"/>
+      <c r="AC175" s="11" t="n"/>
+      <c r="AD175" s="11" t="n"/>
+      <c r="AE175" s="11" t="n"/>
+      <c r="AF175" s="11" t="n"/>
+      <c r="AG175" s="11" t="n"/>
+      <c r="AH175" s="11" t="n"/>
+      <c r="AI175" s="11" t="n"/>
+      <c r="AJ175" s="11" t="n"/>
+      <c r="AK175" s="11" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -6265,6 +8470,18 @@
       <c r="W176" s="11" t="n"/>
       <c r="X176" s="11" t="n"/>
       <c r="Y176" s="11" t="n"/>
+      <c r="Z176" s="11" t="n"/>
+      <c r="AA176" s="11" t="n"/>
+      <c r="AB176" s="11" t="n"/>
+      <c r="AC176" s="11" t="n"/>
+      <c r="AD176" s="11" t="n"/>
+      <c r="AE176" s="11" t="n"/>
+      <c r="AF176" s="11" t="n"/>
+      <c r="AG176" s="11" t="n"/>
+      <c r="AH176" s="11" t="n"/>
+      <c r="AI176" s="11" t="n"/>
+      <c r="AJ176" s="11" t="n"/>
+      <c r="AK176" s="11" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -6296,6 +8513,18 @@
       <c r="W177" s="11" t="n"/>
       <c r="X177" s="11" t="n"/>
       <c r="Y177" s="11" t="n"/>
+      <c r="Z177" s="11" t="n"/>
+      <c r="AA177" s="11" t="n"/>
+      <c r="AB177" s="11" t="n"/>
+      <c r="AC177" s="11" t="n"/>
+      <c r="AD177" s="11" t="n"/>
+      <c r="AE177" s="11" t="n"/>
+      <c r="AF177" s="11" t="n"/>
+      <c r="AG177" s="11" t="n"/>
+      <c r="AH177" s="11" t="n"/>
+      <c r="AI177" s="11" t="n"/>
+      <c r="AJ177" s="11" t="n"/>
+      <c r="AK177" s="11" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -6327,6 +8556,18 @@
       <c r="W178" s="11" t="n"/>
       <c r="X178" s="11" t="n"/>
       <c r="Y178" s="11" t="n"/>
+      <c r="Z178" s="11" t="n"/>
+      <c r="AA178" s="11" t="n"/>
+      <c r="AB178" s="11" t="n"/>
+      <c r="AC178" s="11" t="n"/>
+      <c r="AD178" s="11" t="n"/>
+      <c r="AE178" s="11" t="n"/>
+      <c r="AF178" s="11" t="n"/>
+      <c r="AG178" s="11" t="n"/>
+      <c r="AH178" s="11" t="n"/>
+      <c r="AI178" s="11" t="n"/>
+      <c r="AJ178" s="11" t="n"/>
+      <c r="AK178" s="11" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -6358,6 +8599,18 @@
       <c r="W179" s="11" t="n"/>
       <c r="X179" s="11" t="n"/>
       <c r="Y179" s="11" t="n"/>
+      <c r="Z179" s="11" t="n"/>
+      <c r="AA179" s="11" t="n"/>
+      <c r="AB179" s="11" t="n"/>
+      <c r="AC179" s="11" t="n"/>
+      <c r="AD179" s="11" t="n"/>
+      <c r="AE179" s="11" t="n"/>
+      <c r="AF179" s="11" t="n"/>
+      <c r="AG179" s="11" t="n"/>
+      <c r="AH179" s="11" t="n"/>
+      <c r="AI179" s="11" t="n"/>
+      <c r="AJ179" s="11" t="n"/>
+      <c r="AK179" s="11" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -6389,6 +8642,18 @@
       <c r="W180" s="11" t="n"/>
       <c r="X180" s="11" t="n"/>
       <c r="Y180" s="11" t="n"/>
+      <c r="Z180" s="11" t="n"/>
+      <c r="AA180" s="11" t="n"/>
+      <c r="AB180" s="11" t="n"/>
+      <c r="AC180" s="11" t="n"/>
+      <c r="AD180" s="11" t="n"/>
+      <c r="AE180" s="11" t="n"/>
+      <c r="AF180" s="11" t="n"/>
+      <c r="AG180" s="11" t="n"/>
+      <c r="AH180" s="11" t="n"/>
+      <c r="AI180" s="11" t="n"/>
+      <c r="AJ180" s="11" t="n"/>
+      <c r="AK180" s="11" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -6420,6 +8685,18 @@
       <c r="W181" s="11" t="n"/>
       <c r="X181" s="11" t="n"/>
       <c r="Y181" s="11" t="n"/>
+      <c r="Z181" s="11" t="n"/>
+      <c r="AA181" s="11" t="n"/>
+      <c r="AB181" s="11" t="n"/>
+      <c r="AC181" s="11" t="n"/>
+      <c r="AD181" s="11" t="n"/>
+      <c r="AE181" s="11" t="n"/>
+      <c r="AF181" s="11" t="n"/>
+      <c r="AG181" s="11" t="n"/>
+      <c r="AH181" s="11" t="n"/>
+      <c r="AI181" s="11" t="n"/>
+      <c r="AJ181" s="11" t="n"/>
+      <c r="AK181" s="11" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -6451,6 +8728,18 @@
       <c r="W182" s="11" t="n"/>
       <c r="X182" s="11" t="n"/>
       <c r="Y182" s="11" t="n"/>
+      <c r="Z182" s="11" t="n"/>
+      <c r="AA182" s="11" t="n"/>
+      <c r="AB182" s="11" t="n"/>
+      <c r="AC182" s="11" t="n"/>
+      <c r="AD182" s="11" t="n"/>
+      <c r="AE182" s="11" t="n"/>
+      <c r="AF182" s="11" t="n"/>
+      <c r="AG182" s="11" t="n"/>
+      <c r="AH182" s="11" t="n"/>
+      <c r="AI182" s="11" t="n"/>
+      <c r="AJ182" s="11" t="n"/>
+      <c r="AK182" s="11" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -6482,6 +8771,18 @@
       <c r="W183" s="11" t="n"/>
       <c r="X183" s="11" t="n"/>
       <c r="Y183" s="11" t="n"/>
+      <c r="Z183" s="11" t="n"/>
+      <c r="AA183" s="11" t="n"/>
+      <c r="AB183" s="11" t="n"/>
+      <c r="AC183" s="11" t="n"/>
+      <c r="AD183" s="11" t="n"/>
+      <c r="AE183" s="11" t="n"/>
+      <c r="AF183" s="11" t="n"/>
+      <c r="AG183" s="11" t="n"/>
+      <c r="AH183" s="11" t="n"/>
+      <c r="AI183" s="11" t="n"/>
+      <c r="AJ183" s="11" t="n"/>
+      <c r="AK183" s="11" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -6513,6 +8814,18 @@
       <c r="W184" s="11" t="n"/>
       <c r="X184" s="11" t="n"/>
       <c r="Y184" s="11" t="n"/>
+      <c r="Z184" s="11" t="n"/>
+      <c r="AA184" s="11" t="n"/>
+      <c r="AB184" s="11" t="n"/>
+      <c r="AC184" s="11" t="n"/>
+      <c r="AD184" s="11" t="n"/>
+      <c r="AE184" s="11" t="n"/>
+      <c r="AF184" s="11" t="n"/>
+      <c r="AG184" s="11" t="n"/>
+      <c r="AH184" s="11" t="n"/>
+      <c r="AI184" s="11" t="n"/>
+      <c r="AJ184" s="11" t="n"/>
+      <c r="AK184" s="11" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -6544,6 +8857,18 @@
       <c r="W185" s="11" t="n"/>
       <c r="X185" s="11" t="n"/>
       <c r="Y185" s="11" t="n"/>
+      <c r="Z185" s="11" t="n"/>
+      <c r="AA185" s="11" t="n"/>
+      <c r="AB185" s="11" t="n"/>
+      <c r="AC185" s="11" t="n"/>
+      <c r="AD185" s="11" t="n"/>
+      <c r="AE185" s="11" t="n"/>
+      <c r="AF185" s="11" t="n"/>
+      <c r="AG185" s="11" t="n"/>
+      <c r="AH185" s="11" t="n"/>
+      <c r="AI185" s="11" t="n"/>
+      <c r="AJ185" s="11" t="n"/>
+      <c r="AK185" s="11" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -6575,6 +8900,18 @@
       <c r="W186" s="11" t="n"/>
       <c r="X186" s="11" t="n"/>
       <c r="Y186" s="11" t="n"/>
+      <c r="Z186" s="11" t="n"/>
+      <c r="AA186" s="11" t="n"/>
+      <c r="AB186" s="11" t="n"/>
+      <c r="AC186" s="11" t="n"/>
+      <c r="AD186" s="11" t="n"/>
+      <c r="AE186" s="11" t="n"/>
+      <c r="AF186" s="11" t="n"/>
+      <c r="AG186" s="11" t="n"/>
+      <c r="AH186" s="11" t="n"/>
+      <c r="AI186" s="11" t="n"/>
+      <c r="AJ186" s="11" t="n"/>
+      <c r="AK186" s="11" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -6606,6 +8943,18 @@
       <c r="W187" s="11" t="n"/>
       <c r="X187" s="11" t="n"/>
       <c r="Y187" s="11" t="n"/>
+      <c r="Z187" s="11" t="n"/>
+      <c r="AA187" s="11" t="n"/>
+      <c r="AB187" s="11" t="n"/>
+      <c r="AC187" s="11" t="n"/>
+      <c r="AD187" s="11" t="n"/>
+      <c r="AE187" s="11" t="n"/>
+      <c r="AF187" s="11" t="n"/>
+      <c r="AG187" s="11" t="n"/>
+      <c r="AH187" s="11" t="n"/>
+      <c r="AI187" s="11" t="n"/>
+      <c r="AJ187" s="11" t="n"/>
+      <c r="AK187" s="11" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -6637,6 +8986,18 @@
       <c r="W188" s="11" t="n"/>
       <c r="X188" s="11" t="n"/>
       <c r="Y188" s="11" t="n"/>
+      <c r="Z188" s="11" t="n"/>
+      <c r="AA188" s="11" t="n"/>
+      <c r="AB188" s="11" t="n"/>
+      <c r="AC188" s="11" t="n"/>
+      <c r="AD188" s="11" t="n"/>
+      <c r="AE188" s="11" t="n"/>
+      <c r="AF188" s="11" t="n"/>
+      <c r="AG188" s="11" t="n"/>
+      <c r="AH188" s="11" t="n"/>
+      <c r="AI188" s="11" t="n"/>
+      <c r="AJ188" s="11" t="n"/>
+      <c r="AK188" s="11" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -6668,6 +9029,18 @@
       <c r="W189" s="11" t="n"/>
       <c r="X189" s="11" t="n"/>
       <c r="Y189" s="11" t="n"/>
+      <c r="Z189" s="11" t="n"/>
+      <c r="AA189" s="11" t="n"/>
+      <c r="AB189" s="11" t="n"/>
+      <c r="AC189" s="11" t="n"/>
+      <c r="AD189" s="11" t="n"/>
+      <c r="AE189" s="11" t="n"/>
+      <c r="AF189" s="11" t="n"/>
+      <c r="AG189" s="11" t="n"/>
+      <c r="AH189" s="11" t="n"/>
+      <c r="AI189" s="11" t="n"/>
+      <c r="AJ189" s="11" t="n"/>
+      <c r="AK189" s="11" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -6699,6 +9072,18 @@
       <c r="W190" s="11" t="n"/>
       <c r="X190" s="11" t="n"/>
       <c r="Y190" s="11" t="n"/>
+      <c r="Z190" s="11" t="n"/>
+      <c r="AA190" s="11" t="n"/>
+      <c r="AB190" s="11" t="n"/>
+      <c r="AC190" s="11" t="n"/>
+      <c r="AD190" s="11" t="n"/>
+      <c r="AE190" s="11" t="n"/>
+      <c r="AF190" s="11" t="n"/>
+      <c r="AG190" s="11" t="n"/>
+      <c r="AH190" s="11" t="n"/>
+      <c r="AI190" s="11" t="n"/>
+      <c r="AJ190" s="11" t="n"/>
+      <c r="AK190" s="11" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -6730,6 +9115,18 @@
       <c r="W191" s="11" t="n"/>
       <c r="X191" s="11" t="n"/>
       <c r="Y191" s="11" t="n"/>
+      <c r="Z191" s="11" t="n"/>
+      <c r="AA191" s="11" t="n"/>
+      <c r="AB191" s="11" t="n"/>
+      <c r="AC191" s="11" t="n"/>
+      <c r="AD191" s="11" t="n"/>
+      <c r="AE191" s="11" t="n"/>
+      <c r="AF191" s="11" t="n"/>
+      <c r="AG191" s="11" t="n"/>
+      <c r="AH191" s="11" t="n"/>
+      <c r="AI191" s="11" t="n"/>
+      <c r="AJ191" s="11" t="n"/>
+      <c r="AK191" s="11" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -6757,6 +9154,18 @@
       <c r="W192" s="11" t="n"/>
       <c r="X192" s="11" t="n"/>
       <c r="Y192" s="11" t="n"/>
+      <c r="Z192" s="11" t="n"/>
+      <c r="AA192" s="11" t="n"/>
+      <c r="AB192" s="11" t="n"/>
+      <c r="AC192" s="11" t="n"/>
+      <c r="AD192" s="11" t="n"/>
+      <c r="AE192" s="11" t="n"/>
+      <c r="AF192" s="11" t="n"/>
+      <c r="AG192" s="11" t="n"/>
+      <c r="AH192" s="11" t="n"/>
+      <c r="AI192" s="11" t="n"/>
+      <c r="AJ192" s="11" t="n"/>
+      <c r="AK192" s="11" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -6784,6 +9193,18 @@
       <c r="W193" s="11" t="n"/>
       <c r="X193" s="11" t="n"/>
       <c r="Y193" s="11" t="n"/>
+      <c r="Z193" s="11" t="n"/>
+      <c r="AA193" s="11" t="n"/>
+      <c r="AB193" s="11" t="n"/>
+      <c r="AC193" s="11" t="n"/>
+      <c r="AD193" s="11" t="n"/>
+      <c r="AE193" s="11" t="n"/>
+      <c r="AF193" s="11" t="n"/>
+      <c r="AG193" s="11" t="n"/>
+      <c r="AH193" s="11" t="n"/>
+      <c r="AI193" s="11" t="n"/>
+      <c r="AJ193" s="11" t="n"/>
+      <c r="AK193" s="11" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -6811,6 +9232,18 @@
       <c r="W194" s="11" t="n"/>
       <c r="X194" s="11" t="n"/>
       <c r="Y194" s="11" t="n"/>
+      <c r="Z194" s="11" t="n"/>
+      <c r="AA194" s="11" t="n"/>
+      <c r="AB194" s="11" t="n"/>
+      <c r="AC194" s="11" t="n"/>
+      <c r="AD194" s="11" t="n"/>
+      <c r="AE194" s="11" t="n"/>
+      <c r="AF194" s="11" t="n"/>
+      <c r="AG194" s="11" t="n"/>
+      <c r="AH194" s="11" t="n"/>
+      <c r="AI194" s="11" t="n"/>
+      <c r="AJ194" s="11" t="n"/>
+      <c r="AK194" s="11" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -6838,6 +9271,18 @@
       <c r="W195" s="11" t="n"/>
       <c r="X195" s="11" t="n"/>
       <c r="Y195" s="11" t="n"/>
+      <c r="Z195" s="11" t="n"/>
+      <c r="AA195" s="11" t="n"/>
+      <c r="AB195" s="11" t="n"/>
+      <c r="AC195" s="11" t="n"/>
+      <c r="AD195" s="11" t="n"/>
+      <c r="AE195" s="11" t="n"/>
+      <c r="AF195" s="11" t="n"/>
+      <c r="AG195" s="11" t="n"/>
+      <c r="AH195" s="11" t="n"/>
+      <c r="AI195" s="11" t="n"/>
+      <c r="AJ195" s="11" t="n"/>
+      <c r="AK195" s="11" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -6865,6 +9310,18 @@
       <c r="W196" s="11" t="n"/>
       <c r="X196" s="11" t="n"/>
       <c r="Y196" s="11" t="n"/>
+      <c r="Z196" s="11" t="n"/>
+      <c r="AA196" s="11" t="n"/>
+      <c r="AB196" s="11" t="n"/>
+      <c r="AC196" s="11" t="n"/>
+      <c r="AD196" s="11" t="n"/>
+      <c r="AE196" s="11" t="n"/>
+      <c r="AF196" s="11" t="n"/>
+      <c r="AG196" s="11" t="n"/>
+      <c r="AH196" s="11" t="n"/>
+      <c r="AI196" s="11" t="n"/>
+      <c r="AJ196" s="11" t="n"/>
+      <c r="AK196" s="11" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -6892,6 +9349,18 @@
       <c r="W197" s="11" t="n"/>
       <c r="X197" s="11" t="n"/>
       <c r="Y197" s="11" t="n"/>
+      <c r="Z197" s="11" t="n"/>
+      <c r="AA197" s="11" t="n"/>
+      <c r="AB197" s="11" t="n"/>
+      <c r="AC197" s="11" t="n"/>
+      <c r="AD197" s="11" t="n"/>
+      <c r="AE197" s="11" t="n"/>
+      <c r="AF197" s="11" t="n"/>
+      <c r="AG197" s="11" t="n"/>
+      <c r="AH197" s="11" t="n"/>
+      <c r="AI197" s="11" t="n"/>
+      <c r="AJ197" s="11" t="n"/>
+      <c r="AK197" s="11" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -6919,6 +9388,18 @@
       <c r="W198" s="11" t="n"/>
       <c r="X198" s="11" t="n"/>
       <c r="Y198" s="11" t="n"/>
+      <c r="Z198" s="11" t="n"/>
+      <c r="AA198" s="11" t="n"/>
+      <c r="AB198" s="11" t="n"/>
+      <c r="AC198" s="11" t="n"/>
+      <c r="AD198" s="11" t="n"/>
+      <c r="AE198" s="11" t="n"/>
+      <c r="AF198" s="11" t="n"/>
+      <c r="AG198" s="11" t="n"/>
+      <c r="AH198" s="11" t="n"/>
+      <c r="AI198" s="11" t="n"/>
+      <c r="AJ198" s="11" t="n"/>
+      <c r="AK198" s="11" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -6946,6 +9427,18 @@
       <c r="W199" s="11" t="n"/>
       <c r="X199" s="11" t="n"/>
       <c r="Y199" s="11" t="n"/>
+      <c r="Z199" s="11" t="n"/>
+      <c r="AA199" s="11" t="n"/>
+      <c r="AB199" s="11" t="n"/>
+      <c r="AC199" s="11" t="n"/>
+      <c r="AD199" s="11" t="n"/>
+      <c r="AE199" s="11" t="n"/>
+      <c r="AF199" s="11" t="n"/>
+      <c r="AG199" s="11" t="n"/>
+      <c r="AH199" s="11" t="n"/>
+      <c r="AI199" s="11" t="n"/>
+      <c r="AJ199" s="11" t="n"/>
+      <c r="AK199" s="11" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -6973,6 +9466,18 @@
       <c r="W200" s="11" t="n"/>
       <c r="X200" s="11" t="n"/>
       <c r="Y200" s="11" t="n"/>
+      <c r="Z200" s="11" t="n"/>
+      <c r="AA200" s="11" t="n"/>
+      <c r="AB200" s="11" t="n"/>
+      <c r="AC200" s="11" t="n"/>
+      <c r="AD200" s="11" t="n"/>
+      <c r="AE200" s="11" t="n"/>
+      <c r="AF200" s="11" t="n"/>
+      <c r="AG200" s="11" t="n"/>
+      <c r="AH200" s="11" t="n"/>
+      <c r="AI200" s="11" t="n"/>
+      <c r="AJ200" s="11" t="n"/>
+      <c r="AK200" s="11" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
@@ -7000,6 +9505,18 @@
       <c r="W201" s="11" t="n"/>
       <c r="X201" s="11" t="n"/>
       <c r="Y201" s="11" t="n"/>
+      <c r="Z201" s="11" t="n"/>
+      <c r="AA201" s="11" t="n"/>
+      <c r="AB201" s="11" t="n"/>
+      <c r="AC201" s="11" t="n"/>
+      <c r="AD201" s="11" t="n"/>
+      <c r="AE201" s="11" t="n"/>
+      <c r="AF201" s="11" t="n"/>
+      <c r="AG201" s="11" t="n"/>
+      <c r="AH201" s="11" t="n"/>
+      <c r="AI201" s="11" t="n"/>
+      <c r="AJ201" s="11" t="n"/>
+      <c r="AK201" s="11" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
@@ -7027,6 +9544,18 @@
       <c r="W202" s="11" t="n"/>
       <c r="X202" s="11" t="n"/>
       <c r="Y202" s="11" t="n"/>
+      <c r="Z202" s="11" t="n"/>
+      <c r="AA202" s="11" t="n"/>
+      <c r="AB202" s="11" t="n"/>
+      <c r="AC202" s="11" t="n"/>
+      <c r="AD202" s="11" t="n"/>
+      <c r="AE202" s="11" t="n"/>
+      <c r="AF202" s="11" t="n"/>
+      <c r="AG202" s="11" t="n"/>
+      <c r="AH202" s="11" t="n"/>
+      <c r="AI202" s="11" t="n"/>
+      <c r="AJ202" s="11" t="n"/>
+      <c r="AK202" s="11" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n"/>
@@ -7054,6 +9583,18 @@
       <c r="W203" s="11" t="n"/>
       <c r="X203" s="11" t="n"/>
       <c r="Y203" s="11" t="n"/>
+      <c r="Z203" s="11" t="n"/>
+      <c r="AA203" s="11" t="n"/>
+      <c r="AB203" s="11" t="n"/>
+      <c r="AC203" s="11" t="n"/>
+      <c r="AD203" s="11" t="n"/>
+      <c r="AE203" s="11" t="n"/>
+      <c r="AF203" s="11" t="n"/>
+      <c r="AG203" s="11" t="n"/>
+      <c r="AH203" s="11" t="n"/>
+      <c r="AI203" s="11" t="n"/>
+      <c r="AJ203" s="11" t="n"/>
+      <c r="AK203" s="11" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n"/>
@@ -7081,6 +9622,18 @@
       <c r="W204" s="11" t="n"/>
       <c r="X204" s="11" t="n"/>
       <c r="Y204" s="11" t="n"/>
+      <c r="Z204" s="11" t="n"/>
+      <c r="AA204" s="11" t="n"/>
+      <c r="AB204" s="11" t="n"/>
+      <c r="AC204" s="11" t="n"/>
+      <c r="AD204" s="11" t="n"/>
+      <c r="AE204" s="11" t="n"/>
+      <c r="AF204" s="11" t="n"/>
+      <c r="AG204" s="11" t="n"/>
+      <c r="AH204" s="11" t="n"/>
+      <c r="AI204" s="11" t="n"/>
+      <c r="AJ204" s="11" t="n"/>
+      <c r="AK204" s="11" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n"/>
@@ -7108,6 +9661,18 @@
       <c r="W205" s="11" t="n"/>
       <c r="X205" s="11" t="n"/>
       <c r="Y205" s="11" t="n"/>
+      <c r="Z205" s="11" t="n"/>
+      <c r="AA205" s="11" t="n"/>
+      <c r="AB205" s="11" t="n"/>
+      <c r="AC205" s="11" t="n"/>
+      <c r="AD205" s="11" t="n"/>
+      <c r="AE205" s="11" t="n"/>
+      <c r="AF205" s="11" t="n"/>
+      <c r="AG205" s="11" t="n"/>
+      <c r="AH205" s="11" t="n"/>
+      <c r="AI205" s="11" t="n"/>
+      <c r="AJ205" s="11" t="n"/>
+      <c r="AK205" s="11" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n"/>
@@ -7135,6 +9700,18 @@
       <c r="W206" s="11" t="n"/>
       <c r="X206" s="11" t="n"/>
       <c r="Y206" s="11" t="n"/>
+      <c r="Z206" s="11" t="n"/>
+      <c r="AA206" s="11" t="n"/>
+      <c r="AB206" s="11" t="n"/>
+      <c r="AC206" s="11" t="n"/>
+      <c r="AD206" s="11" t="n"/>
+      <c r="AE206" s="11" t="n"/>
+      <c r="AF206" s="11" t="n"/>
+      <c r="AG206" s="11" t="n"/>
+      <c r="AH206" s="11" t="n"/>
+      <c r="AI206" s="11" t="n"/>
+      <c r="AJ206" s="11" t="n"/>
+      <c r="AK206" s="11" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n"/>
@@ -7162,6 +9739,18 @@
       <c r="W207" s="11" t="n"/>
       <c r="X207" s="11" t="n"/>
       <c r="Y207" s="11" t="n"/>
+      <c r="Z207" s="11" t="n"/>
+      <c r="AA207" s="11" t="n"/>
+      <c r="AB207" s="11" t="n"/>
+      <c r="AC207" s="11" t="n"/>
+      <c r="AD207" s="11" t="n"/>
+      <c r="AE207" s="11" t="n"/>
+      <c r="AF207" s="11" t="n"/>
+      <c r="AG207" s="11" t="n"/>
+      <c r="AH207" s="11" t="n"/>
+      <c r="AI207" s="11" t="n"/>
+      <c r="AJ207" s="11" t="n"/>
+      <c r="AK207" s="11" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n"/>
@@ -7189,6 +9778,18 @@
       <c r="W208" s="11" t="n"/>
       <c r="X208" s="11" t="n"/>
       <c r="Y208" s="11" t="n"/>
+      <c r="Z208" s="11" t="n"/>
+      <c r="AA208" s="11" t="n"/>
+      <c r="AB208" s="11" t="n"/>
+      <c r="AC208" s="11" t="n"/>
+      <c r="AD208" s="11" t="n"/>
+      <c r="AE208" s="11" t="n"/>
+      <c r="AF208" s="11" t="n"/>
+      <c r="AG208" s="11" t="n"/>
+      <c r="AH208" s="11" t="n"/>
+      <c r="AI208" s="11" t="n"/>
+      <c r="AJ208" s="11" t="n"/>
+      <c r="AK208" s="11" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n"/>
@@ -7216,6 +9817,18 @@
       <c r="W209" s="11" t="n"/>
       <c r="X209" s="11" t="n"/>
       <c r="Y209" s="11" t="n"/>
+      <c r="Z209" s="11" t="n"/>
+      <c r="AA209" s="11" t="n"/>
+      <c r="AB209" s="11" t="n"/>
+      <c r="AC209" s="11" t="n"/>
+      <c r="AD209" s="11" t="n"/>
+      <c r="AE209" s="11" t="n"/>
+      <c r="AF209" s="11" t="n"/>
+      <c r="AG209" s="11" t="n"/>
+      <c r="AH209" s="11" t="n"/>
+      <c r="AI209" s="11" t="n"/>
+      <c r="AJ209" s="11" t="n"/>
+      <c r="AK209" s="11" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n"/>
@@ -7243,6 +9856,18 @@
       <c r="W210" s="11" t="n"/>
       <c r="X210" s="11" t="n"/>
       <c r="Y210" s="11" t="n"/>
+      <c r="Z210" s="11" t="n"/>
+      <c r="AA210" s="11" t="n"/>
+      <c r="AB210" s="11" t="n"/>
+      <c r="AC210" s="11" t="n"/>
+      <c r="AD210" s="11" t="n"/>
+      <c r="AE210" s="11" t="n"/>
+      <c r="AF210" s="11" t="n"/>
+      <c r="AG210" s="11" t="n"/>
+      <c r="AH210" s="11" t="n"/>
+      <c r="AI210" s="11" t="n"/>
+      <c r="AJ210" s="11" t="n"/>
+      <c r="AK210" s="11" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n"/>
@@ -7270,6 +9895,18 @@
       <c r="W211" s="11" t="n"/>
       <c r="X211" s="11" t="n"/>
       <c r="Y211" s="11" t="n"/>
+      <c r="Z211" s="11" t="n"/>
+      <c r="AA211" s="11" t="n"/>
+      <c r="AB211" s="11" t="n"/>
+      <c r="AC211" s="11" t="n"/>
+      <c r="AD211" s="11" t="n"/>
+      <c r="AE211" s="11" t="n"/>
+      <c r="AF211" s="11" t="n"/>
+      <c r="AG211" s="11" t="n"/>
+      <c r="AH211" s="11" t="n"/>
+      <c r="AI211" s="11" t="n"/>
+      <c r="AJ211" s="11" t="n"/>
+      <c r="AK211" s="11" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n"/>
@@ -7297,6 +9934,18 @@
       <c r="W212" s="11" t="n"/>
       <c r="X212" s="11" t="n"/>
       <c r="Y212" s="11" t="n"/>
+      <c r="Z212" s="11" t="n"/>
+      <c r="AA212" s="11" t="n"/>
+      <c r="AB212" s="11" t="n"/>
+      <c r="AC212" s="11" t="n"/>
+      <c r="AD212" s="11" t="n"/>
+      <c r="AE212" s="11" t="n"/>
+      <c r="AF212" s="11" t="n"/>
+      <c r="AG212" s="11" t="n"/>
+      <c r="AH212" s="11" t="n"/>
+      <c r="AI212" s="11" t="n"/>
+      <c r="AJ212" s="11" t="n"/>
+      <c r="AK212" s="11" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n"/>
@@ -7324,6 +9973,18 @@
       <c r="W213" s="11" t="n"/>
       <c r="X213" s="11" t="n"/>
       <c r="Y213" s="11" t="n"/>
+      <c r="Z213" s="11" t="n"/>
+      <c r="AA213" s="11" t="n"/>
+      <c r="AB213" s="11" t="n"/>
+      <c r="AC213" s="11" t="n"/>
+      <c r="AD213" s="11" t="n"/>
+      <c r="AE213" s="11" t="n"/>
+      <c r="AF213" s="11" t="n"/>
+      <c r="AG213" s="11" t="n"/>
+      <c r="AH213" s="11" t="n"/>
+      <c r="AI213" s="11" t="n"/>
+      <c r="AJ213" s="11" t="n"/>
+      <c r="AK213" s="11" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n"/>
@@ -7351,6 +10012,18 @@
       <c r="W214" s="11" t="n"/>
       <c r="X214" s="11" t="n"/>
       <c r="Y214" s="11" t="n"/>
+      <c r="Z214" s="11" t="n"/>
+      <c r="AA214" s="11" t="n"/>
+      <c r="AB214" s="11" t="n"/>
+      <c r="AC214" s="11" t="n"/>
+      <c r="AD214" s="11" t="n"/>
+      <c r="AE214" s="11" t="n"/>
+      <c r="AF214" s="11" t="n"/>
+      <c r="AG214" s="11" t="n"/>
+      <c r="AH214" s="11" t="n"/>
+      <c r="AI214" s="11" t="n"/>
+      <c r="AJ214" s="11" t="n"/>
+      <c r="AK214" s="11" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="n"/>
@@ -7378,6 +10051,18 @@
       <c r="W215" s="11" t="n"/>
       <c r="X215" s="11" t="n"/>
       <c r="Y215" s="11" t="n"/>
+      <c r="Z215" s="11" t="n"/>
+      <c r="AA215" s="11" t="n"/>
+      <c r="AB215" s="11" t="n"/>
+      <c r="AC215" s="11" t="n"/>
+      <c r="AD215" s="11" t="n"/>
+      <c r="AE215" s="11" t="n"/>
+      <c r="AF215" s="11" t="n"/>
+      <c r="AG215" s="11" t="n"/>
+      <c r="AH215" s="11" t="n"/>
+      <c r="AI215" s="11" t="n"/>
+      <c r="AJ215" s="11" t="n"/>
+      <c r="AK215" s="11" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
@@ -7405,6 +10090,18 @@
       <c r="W216" s="11" t="n"/>
       <c r="X216" s="11" t="n"/>
       <c r="Y216" s="11" t="n"/>
+      <c r="Z216" s="11" t="n"/>
+      <c r="AA216" s="11" t="n"/>
+      <c r="AB216" s="11" t="n"/>
+      <c r="AC216" s="11" t="n"/>
+      <c r="AD216" s="11" t="n"/>
+      <c r="AE216" s="11" t="n"/>
+      <c r="AF216" s="11" t="n"/>
+      <c r="AG216" s="11" t="n"/>
+      <c r="AH216" s="11" t="n"/>
+      <c r="AI216" s="11" t="n"/>
+      <c r="AJ216" s="11" t="n"/>
+      <c r="AK216" s="11" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
@@ -7432,6 +10129,18 @@
       <c r="W217" s="11" t="n"/>
       <c r="X217" s="11" t="n"/>
       <c r="Y217" s="11" t="n"/>
+      <c r="Z217" s="11" t="n"/>
+      <c r="AA217" s="11" t="n"/>
+      <c r="AB217" s="11" t="n"/>
+      <c r="AC217" s="11" t="n"/>
+      <c r="AD217" s="11" t="n"/>
+      <c r="AE217" s="11" t="n"/>
+      <c r="AF217" s="11" t="n"/>
+      <c r="AG217" s="11" t="n"/>
+      <c r="AH217" s="11" t="n"/>
+      <c r="AI217" s="11" t="n"/>
+      <c r="AJ217" s="11" t="n"/>
+      <c r="AK217" s="11" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n"/>
@@ -7459,6 +10168,18 @@
       <c r="W218" s="11" t="n"/>
       <c r="X218" s="11" t="n"/>
       <c r="Y218" s="11" t="n"/>
+      <c r="Z218" s="11" t="n"/>
+      <c r="AA218" s="11" t="n"/>
+      <c r="AB218" s="11" t="n"/>
+      <c r="AC218" s="11" t="n"/>
+      <c r="AD218" s="11" t="n"/>
+      <c r="AE218" s="11" t="n"/>
+      <c r="AF218" s="11" t="n"/>
+      <c r="AG218" s="11" t="n"/>
+      <c r="AH218" s="11" t="n"/>
+      <c r="AI218" s="11" t="n"/>
+      <c r="AJ218" s="11" t="n"/>
+      <c r="AK218" s="11" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n"/>
@@ -7486,6 +10207,18 @@
       <c r="W219" s="11" t="n"/>
       <c r="X219" s="11" t="n"/>
       <c r="Y219" s="11" t="n"/>
+      <c r="Z219" s="11" t="n"/>
+      <c r="AA219" s="11" t="n"/>
+      <c r="AB219" s="11" t="n"/>
+      <c r="AC219" s="11" t="n"/>
+      <c r="AD219" s="11" t="n"/>
+      <c r="AE219" s="11" t="n"/>
+      <c r="AF219" s="11" t="n"/>
+      <c r="AG219" s="11" t="n"/>
+      <c r="AH219" s="11" t="n"/>
+      <c r="AI219" s="11" t="n"/>
+      <c r="AJ219" s="11" t="n"/>
+      <c r="AK219" s="11" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n"/>
@@ -7513,6 +10246,18 @@
       <c r="W220" s="11" t="n"/>
       <c r="X220" s="11" t="n"/>
       <c r="Y220" s="11" t="n"/>
+      <c r="Z220" s="11" t="n"/>
+      <c r="AA220" s="11" t="n"/>
+      <c r="AB220" s="11" t="n"/>
+      <c r="AC220" s="11" t="n"/>
+      <c r="AD220" s="11" t="n"/>
+      <c r="AE220" s="11" t="n"/>
+      <c r="AF220" s="11" t="n"/>
+      <c r="AG220" s="11" t="n"/>
+      <c r="AH220" s="11" t="n"/>
+      <c r="AI220" s="11" t="n"/>
+      <c r="AJ220" s="11" t="n"/>
+      <c r="AK220" s="11" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
@@ -7540,6 +10285,18 @@
       <c r="W221" s="11" t="n"/>
       <c r="X221" s="11" t="n"/>
       <c r="Y221" s="11" t="n"/>
+      <c r="Z221" s="11" t="n"/>
+      <c r="AA221" s="11" t="n"/>
+      <c r="AB221" s="11" t="n"/>
+      <c r="AC221" s="11" t="n"/>
+      <c r="AD221" s="11" t="n"/>
+      <c r="AE221" s="11" t="n"/>
+      <c r="AF221" s="11" t="n"/>
+      <c r="AG221" s="11" t="n"/>
+      <c r="AH221" s="11" t="n"/>
+      <c r="AI221" s="11" t="n"/>
+      <c r="AJ221" s="11" t="n"/>
+      <c r="AK221" s="11" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n"/>
@@ -7567,6 +10324,18 @@
       <c r="W222" s="11" t="n"/>
       <c r="X222" s="11" t="n"/>
       <c r="Y222" s="11" t="n"/>
+      <c r="Z222" s="11" t="n"/>
+      <c r="AA222" s="11" t="n"/>
+      <c r="AB222" s="11" t="n"/>
+      <c r="AC222" s="11" t="n"/>
+      <c r="AD222" s="11" t="n"/>
+      <c r="AE222" s="11" t="n"/>
+      <c r="AF222" s="11" t="n"/>
+      <c r="AG222" s="11" t="n"/>
+      <c r="AH222" s="11" t="n"/>
+      <c r="AI222" s="11" t="n"/>
+      <c r="AJ222" s="11" t="n"/>
+      <c r="AK222" s="11" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n"/>
@@ -7594,6 +10363,18 @@
       <c r="W223" s="11" t="n"/>
       <c r="X223" s="11" t="n"/>
       <c r="Y223" s="11" t="n"/>
+      <c r="Z223" s="11" t="n"/>
+      <c r="AA223" s="11" t="n"/>
+      <c r="AB223" s="11" t="n"/>
+      <c r="AC223" s="11" t="n"/>
+      <c r="AD223" s="11" t="n"/>
+      <c r="AE223" s="11" t="n"/>
+      <c r="AF223" s="11" t="n"/>
+      <c r="AG223" s="11" t="n"/>
+      <c r="AH223" s="11" t="n"/>
+      <c r="AI223" s="11" t="n"/>
+      <c r="AJ223" s="11" t="n"/>
+      <c r="AK223" s="11" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
@@ -7621,6 +10402,18 @@
       <c r="W224" s="11" t="n"/>
       <c r="X224" s="11" t="n"/>
       <c r="Y224" s="11" t="n"/>
+      <c r="Z224" s="11" t="n"/>
+      <c r="AA224" s="11" t="n"/>
+      <c r="AB224" s="11" t="n"/>
+      <c r="AC224" s="11" t="n"/>
+      <c r="AD224" s="11" t="n"/>
+      <c r="AE224" s="11" t="n"/>
+      <c r="AF224" s="11" t="n"/>
+      <c r="AG224" s="11" t="n"/>
+      <c r="AH224" s="11" t="n"/>
+      <c r="AI224" s="11" t="n"/>
+      <c r="AJ224" s="11" t="n"/>
+      <c r="AK224" s="11" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
@@ -7648,6 +10441,18 @@
       <c r="W225" s="11" t="n"/>
       <c r="X225" s="11" t="n"/>
       <c r="Y225" s="11" t="n"/>
+      <c r="Z225" s="11" t="n"/>
+      <c r="AA225" s="11" t="n"/>
+      <c r="AB225" s="11" t="n"/>
+      <c r="AC225" s="11" t="n"/>
+      <c r="AD225" s="11" t="n"/>
+      <c r="AE225" s="11" t="n"/>
+      <c r="AF225" s="11" t="n"/>
+      <c r="AG225" s="11" t="n"/>
+      <c r="AH225" s="11" t="n"/>
+      <c r="AI225" s="11" t="n"/>
+      <c r="AJ225" s="11" t="n"/>
+      <c r="AK225" s="11" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
@@ -7675,6 +10480,18 @@
       <c r="W226" s="11" t="n"/>
       <c r="X226" s="11" t="n"/>
       <c r="Y226" s="11" t="n"/>
+      <c r="Z226" s="11" t="n"/>
+      <c r="AA226" s="11" t="n"/>
+      <c r="AB226" s="11" t="n"/>
+      <c r="AC226" s="11" t="n"/>
+      <c r="AD226" s="11" t="n"/>
+      <c r="AE226" s="11" t="n"/>
+      <c r="AF226" s="11" t="n"/>
+      <c r="AG226" s="11" t="n"/>
+      <c r="AH226" s="11" t="n"/>
+      <c r="AI226" s="11" t="n"/>
+      <c r="AJ226" s="11" t="n"/>
+      <c r="AK226" s="11" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n"/>
@@ -7702,6 +10519,18 @@
       <c r="W227" s="11" t="n"/>
       <c r="X227" s="11" t="n"/>
       <c r="Y227" s="11" t="n"/>
+      <c r="Z227" s="11" t="n"/>
+      <c r="AA227" s="11" t="n"/>
+      <c r="AB227" s="11" t="n"/>
+      <c r="AC227" s="11" t="n"/>
+      <c r="AD227" s="11" t="n"/>
+      <c r="AE227" s="11" t="n"/>
+      <c r="AF227" s="11" t="n"/>
+      <c r="AG227" s="11" t="n"/>
+      <c r="AH227" s="11" t="n"/>
+      <c r="AI227" s="11" t="n"/>
+      <c r="AJ227" s="11" t="n"/>
+      <c r="AK227" s="11" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n"/>
@@ -7729,6 +10558,18 @@
       <c r="W228" s="11" t="n"/>
       <c r="X228" s="11" t="n"/>
       <c r="Y228" s="11" t="n"/>
+      <c r="Z228" s="11" t="n"/>
+      <c r="AA228" s="11" t="n"/>
+      <c r="AB228" s="11" t="n"/>
+      <c r="AC228" s="11" t="n"/>
+      <c r="AD228" s="11" t="n"/>
+      <c r="AE228" s="11" t="n"/>
+      <c r="AF228" s="11" t="n"/>
+      <c r="AG228" s="11" t="n"/>
+      <c r="AH228" s="11" t="n"/>
+      <c r="AI228" s="11" t="n"/>
+      <c r="AJ228" s="11" t="n"/>
+      <c r="AK228" s="11" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n"/>
@@ -7756,6 +10597,18 @@
       <c r="W229" s="11" t="n"/>
       <c r="X229" s="11" t="n"/>
       <c r="Y229" s="11" t="n"/>
+      <c r="Z229" s="11" t="n"/>
+      <c r="AA229" s="11" t="n"/>
+      <c r="AB229" s="11" t="n"/>
+      <c r="AC229" s="11" t="n"/>
+      <c r="AD229" s="11" t="n"/>
+      <c r="AE229" s="11" t="n"/>
+      <c r="AF229" s="11" t="n"/>
+      <c r="AG229" s="11" t="n"/>
+      <c r="AH229" s="11" t="n"/>
+      <c r="AI229" s="11" t="n"/>
+      <c r="AJ229" s="11" t="n"/>
+      <c r="AK229" s="11" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n"/>
@@ -7783,6 +10636,18 @@
       <c r="W230" s="11" t="n"/>
       <c r="X230" s="11" t="n"/>
       <c r="Y230" s="11" t="n"/>
+      <c r="Z230" s="11" t="n"/>
+      <c r="AA230" s="11" t="n"/>
+      <c r="AB230" s="11" t="n"/>
+      <c r="AC230" s="11" t="n"/>
+      <c r="AD230" s="11" t="n"/>
+      <c r="AE230" s="11" t="n"/>
+      <c r="AF230" s="11" t="n"/>
+      <c r="AG230" s="11" t="n"/>
+      <c r="AH230" s="11" t="n"/>
+      <c r="AI230" s="11" t="n"/>
+      <c r="AJ230" s="11" t="n"/>
+      <c r="AK230" s="11" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n"/>
@@ -7810,6 +10675,18 @@
       <c r="W231" s="11" t="n"/>
       <c r="X231" s="11" t="n"/>
       <c r="Y231" s="11" t="n"/>
+      <c r="Z231" s="11" t="n"/>
+      <c r="AA231" s="11" t="n"/>
+      <c r="AB231" s="11" t="n"/>
+      <c r="AC231" s="11" t="n"/>
+      <c r="AD231" s="11" t="n"/>
+      <c r="AE231" s="11" t="n"/>
+      <c r="AF231" s="11" t="n"/>
+      <c r="AG231" s="11" t="n"/>
+      <c r="AH231" s="11" t="n"/>
+      <c r="AI231" s="11" t="n"/>
+      <c r="AJ231" s="11" t="n"/>
+      <c r="AK231" s="11" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
@@ -7837,6 +10714,18 @@
       <c r="W232" s="11" t="n"/>
       <c r="X232" s="11" t="n"/>
       <c r="Y232" s="11" t="n"/>
+      <c r="Z232" s="11" t="n"/>
+      <c r="AA232" s="11" t="n"/>
+      <c r="AB232" s="11" t="n"/>
+      <c r="AC232" s="11" t="n"/>
+      <c r="AD232" s="11" t="n"/>
+      <c r="AE232" s="11" t="n"/>
+      <c r="AF232" s="11" t="n"/>
+      <c r="AG232" s="11" t="n"/>
+      <c r="AH232" s="11" t="n"/>
+      <c r="AI232" s="11" t="n"/>
+      <c r="AJ232" s="11" t="n"/>
+      <c r="AK232" s="11" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
@@ -7864,6 +10753,18 @@
       <c r="W233" s="11" t="n"/>
       <c r="X233" s="11" t="n"/>
       <c r="Y233" s="11" t="n"/>
+      <c r="Z233" s="11" t="n"/>
+      <c r="AA233" s="11" t="n"/>
+      <c r="AB233" s="11" t="n"/>
+      <c r="AC233" s="11" t="n"/>
+      <c r="AD233" s="11" t="n"/>
+      <c r="AE233" s="11" t="n"/>
+      <c r="AF233" s="11" t="n"/>
+      <c r="AG233" s="11" t="n"/>
+      <c r="AH233" s="11" t="n"/>
+      <c r="AI233" s="11" t="n"/>
+      <c r="AJ233" s="11" t="n"/>
+      <c r="AK233" s="11" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n"/>
@@ -7891,6 +10792,18 @@
       <c r="W234" s="11" t="n"/>
       <c r="X234" s="11" t="n"/>
       <c r="Y234" s="11" t="n"/>
+      <c r="Z234" s="11" t="n"/>
+      <c r="AA234" s="11" t="n"/>
+      <c r="AB234" s="11" t="n"/>
+      <c r="AC234" s="11" t="n"/>
+      <c r="AD234" s="11" t="n"/>
+      <c r="AE234" s="11" t="n"/>
+      <c r="AF234" s="11" t="n"/>
+      <c r="AG234" s="11" t="n"/>
+      <c r="AH234" s="11" t="n"/>
+      <c r="AI234" s="11" t="n"/>
+      <c r="AJ234" s="11" t="n"/>
+      <c r="AK234" s="11" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n"/>
@@ -7918,6 +10831,18 @@
       <c r="W235" s="11" t="n"/>
       <c r="X235" s="11" t="n"/>
       <c r="Y235" s="11" t="n"/>
+      <c r="Z235" s="11" t="n"/>
+      <c r="AA235" s="11" t="n"/>
+      <c r="AB235" s="11" t="n"/>
+      <c r="AC235" s="11" t="n"/>
+      <c r="AD235" s="11" t="n"/>
+      <c r="AE235" s="11" t="n"/>
+      <c r="AF235" s="11" t="n"/>
+      <c r="AG235" s="11" t="n"/>
+      <c r="AH235" s="11" t="n"/>
+      <c r="AI235" s="11" t="n"/>
+      <c r="AJ235" s="11" t="n"/>
+      <c r="AK235" s="11" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="n"/>
@@ -7945,6 +10870,18 @@
       <c r="W236" s="11" t="n"/>
       <c r="X236" s="11" t="n"/>
       <c r="Y236" s="11" t="n"/>
+      <c r="Z236" s="11" t="n"/>
+      <c r="AA236" s="11" t="n"/>
+      <c r="AB236" s="11" t="n"/>
+      <c r="AC236" s="11" t="n"/>
+      <c r="AD236" s="11" t="n"/>
+      <c r="AE236" s="11" t="n"/>
+      <c r="AF236" s="11" t="n"/>
+      <c r="AG236" s="11" t="n"/>
+      <c r="AH236" s="11" t="n"/>
+      <c r="AI236" s="11" t="n"/>
+      <c r="AJ236" s="11" t="n"/>
+      <c r="AK236" s="11" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n"/>
@@ -7972,6 +10909,18 @@
       <c r="W237" s="11" t="n"/>
       <c r="X237" s="11" t="n"/>
       <c r="Y237" s="11" t="n"/>
+      <c r="Z237" s="11" t="n"/>
+      <c r="AA237" s="11" t="n"/>
+      <c r="AB237" s="11" t="n"/>
+      <c r="AC237" s="11" t="n"/>
+      <c r="AD237" s="11" t="n"/>
+      <c r="AE237" s="11" t="n"/>
+      <c r="AF237" s="11" t="n"/>
+      <c r="AG237" s="11" t="n"/>
+      <c r="AH237" s="11" t="n"/>
+      <c r="AI237" s="11" t="n"/>
+      <c r="AJ237" s="11" t="n"/>
+      <c r="AK237" s="11" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n"/>
@@ -7999,6 +10948,18 @@
       <c r="W238" s="11" t="n"/>
       <c r="X238" s="11" t="n"/>
       <c r="Y238" s="11" t="n"/>
+      <c r="Z238" s="11" t="n"/>
+      <c r="AA238" s="11" t="n"/>
+      <c r="AB238" s="11" t="n"/>
+      <c r="AC238" s="11" t="n"/>
+      <c r="AD238" s="11" t="n"/>
+      <c r="AE238" s="11" t="n"/>
+      <c r="AF238" s="11" t="n"/>
+      <c r="AG238" s="11" t="n"/>
+      <c r="AH238" s="11" t="n"/>
+      <c r="AI238" s="11" t="n"/>
+      <c r="AJ238" s="11" t="n"/>
+      <c r="AK238" s="11" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
@@ -8026,6 +10987,18 @@
       <c r="W239" s="11" t="n"/>
       <c r="X239" s="11" t="n"/>
       <c r="Y239" s="11" t="n"/>
+      <c r="Z239" s="11" t="n"/>
+      <c r="AA239" s="11" t="n"/>
+      <c r="AB239" s="11" t="n"/>
+      <c r="AC239" s="11" t="n"/>
+      <c r="AD239" s="11" t="n"/>
+      <c r="AE239" s="11" t="n"/>
+      <c r="AF239" s="11" t="n"/>
+      <c r="AG239" s="11" t="n"/>
+      <c r="AH239" s="11" t="n"/>
+      <c r="AI239" s="11" t="n"/>
+      <c r="AJ239" s="11" t="n"/>
+      <c r="AK239" s="11" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n"/>
@@ -8053,6 +11026,18 @@
       <c r="W240" s="11" t="n"/>
       <c r="X240" s="11" t="n"/>
       <c r="Y240" s="11" t="n"/>
+      <c r="Z240" s="11" t="n"/>
+      <c r="AA240" s="11" t="n"/>
+      <c r="AB240" s="11" t="n"/>
+      <c r="AC240" s="11" t="n"/>
+      <c r="AD240" s="11" t="n"/>
+      <c r="AE240" s="11" t="n"/>
+      <c r="AF240" s="11" t="n"/>
+      <c r="AG240" s="11" t="n"/>
+      <c r="AH240" s="11" t="n"/>
+      <c r="AI240" s="11" t="n"/>
+      <c r="AJ240" s="11" t="n"/>
+      <c r="AK240" s="11" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n"/>
@@ -8080,6 +11065,18 @@
       <c r="W241" s="11" t="n"/>
       <c r="X241" s="11" t="n"/>
       <c r="Y241" s="11" t="n"/>
+      <c r="Z241" s="11" t="n"/>
+      <c r="AA241" s="11" t="n"/>
+      <c r="AB241" s="11" t="n"/>
+      <c r="AC241" s="11" t="n"/>
+      <c r="AD241" s="11" t="n"/>
+      <c r="AE241" s="11" t="n"/>
+      <c r="AF241" s="11" t="n"/>
+      <c r="AG241" s="11" t="n"/>
+      <c r="AH241" s="11" t="n"/>
+      <c r="AI241" s="11" t="n"/>
+      <c r="AJ241" s="11" t="n"/>
+      <c r="AK241" s="11" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n"/>
@@ -8107,6 +11104,18 @@
       <c r="W242" s="11" t="n"/>
       <c r="X242" s="11" t="n"/>
       <c r="Y242" s="11" t="n"/>
+      <c r="Z242" s="11" t="n"/>
+      <c r="AA242" s="11" t="n"/>
+      <c r="AB242" s="11" t="n"/>
+      <c r="AC242" s="11" t="n"/>
+      <c r="AD242" s="11" t="n"/>
+      <c r="AE242" s="11" t="n"/>
+      <c r="AF242" s="11" t="n"/>
+      <c r="AG242" s="11" t="n"/>
+      <c r="AH242" s="11" t="n"/>
+      <c r="AI242" s="11" t="n"/>
+      <c r="AJ242" s="11" t="n"/>
+      <c r="AK242" s="11" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="n"/>
@@ -8134,6 +11143,18 @@
       <c r="W243" s="11" t="n"/>
       <c r="X243" s="11" t="n"/>
       <c r="Y243" s="11" t="n"/>
+      <c r="Z243" s="11" t="n"/>
+      <c r="AA243" s="11" t="n"/>
+      <c r="AB243" s="11" t="n"/>
+      <c r="AC243" s="11" t="n"/>
+      <c r="AD243" s="11" t="n"/>
+      <c r="AE243" s="11" t="n"/>
+      <c r="AF243" s="11" t="n"/>
+      <c r="AG243" s="11" t="n"/>
+      <c r="AH243" s="11" t="n"/>
+      <c r="AI243" s="11" t="n"/>
+      <c r="AJ243" s="11" t="n"/>
+      <c r="AK243" s="11" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n"/>
@@ -8161,6 +11182,18 @@
       <c r="W244" s="11" t="n"/>
       <c r="X244" s="11" t="n"/>
       <c r="Y244" s="11" t="n"/>
+      <c r="Z244" s="11" t="n"/>
+      <c r="AA244" s="11" t="n"/>
+      <c r="AB244" s="11" t="n"/>
+      <c r="AC244" s="11" t="n"/>
+      <c r="AD244" s="11" t="n"/>
+      <c r="AE244" s="11" t="n"/>
+      <c r="AF244" s="11" t="n"/>
+      <c r="AG244" s="11" t="n"/>
+      <c r="AH244" s="11" t="n"/>
+      <c r="AI244" s="11" t="n"/>
+      <c r="AJ244" s="11" t="n"/>
+      <c r="AK244" s="11" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n"/>
@@ -8188,6 +11221,18 @@
       <c r="W245" s="11" t="n"/>
       <c r="X245" s="11" t="n"/>
       <c r="Y245" s="11" t="n"/>
+      <c r="Z245" s="11" t="n"/>
+      <c r="AA245" s="11" t="n"/>
+      <c r="AB245" s="11" t="n"/>
+      <c r="AC245" s="11" t="n"/>
+      <c r="AD245" s="11" t="n"/>
+      <c r="AE245" s="11" t="n"/>
+      <c r="AF245" s="11" t="n"/>
+      <c r="AG245" s="11" t="n"/>
+      <c r="AH245" s="11" t="n"/>
+      <c r="AI245" s="11" t="n"/>
+      <c r="AJ245" s="11" t="n"/>
+      <c r="AK245" s="11" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n"/>
@@ -8215,6 +11260,18 @@
       <c r="W246" s="11" t="n"/>
       <c r="X246" s="11" t="n"/>
       <c r="Y246" s="11" t="n"/>
+      <c r="Z246" s="11" t="n"/>
+      <c r="AA246" s="11" t="n"/>
+      <c r="AB246" s="11" t="n"/>
+      <c r="AC246" s="11" t="n"/>
+      <c r="AD246" s="11" t="n"/>
+      <c r="AE246" s="11" t="n"/>
+      <c r="AF246" s="11" t="n"/>
+      <c r="AG246" s="11" t="n"/>
+      <c r="AH246" s="11" t="n"/>
+      <c r="AI246" s="11" t="n"/>
+      <c r="AJ246" s="11" t="n"/>
+      <c r="AK246" s="11" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n"/>
@@ -8242,6 +11299,18 @@
       <c r="W247" s="11" t="n"/>
       <c r="X247" s="11" t="n"/>
       <c r="Y247" s="11" t="n"/>
+      <c r="Z247" s="11" t="n"/>
+      <c r="AA247" s="11" t="n"/>
+      <c r="AB247" s="11" t="n"/>
+      <c r="AC247" s="11" t="n"/>
+      <c r="AD247" s="11" t="n"/>
+      <c r="AE247" s="11" t="n"/>
+      <c r="AF247" s="11" t="n"/>
+      <c r="AG247" s="11" t="n"/>
+      <c r="AH247" s="11" t="n"/>
+      <c r="AI247" s="11" t="n"/>
+      <c r="AJ247" s="11" t="n"/>
+      <c r="AK247" s="11" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n"/>
@@ -8269,6 +11338,18 @@
       <c r="W248" s="11" t="n"/>
       <c r="X248" s="11" t="n"/>
       <c r="Y248" s="11" t="n"/>
+      <c r="Z248" s="11" t="n"/>
+      <c r="AA248" s="11" t="n"/>
+      <c r="AB248" s="11" t="n"/>
+      <c r="AC248" s="11" t="n"/>
+      <c r="AD248" s="11" t="n"/>
+      <c r="AE248" s="11" t="n"/>
+      <c r="AF248" s="11" t="n"/>
+      <c r="AG248" s="11" t="n"/>
+      <c r="AH248" s="11" t="n"/>
+      <c r="AI248" s="11" t="n"/>
+      <c r="AJ248" s="11" t="n"/>
+      <c r="AK248" s="11" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n"/>
@@ -8296,6 +11377,18 @@
       <c r="W249" s="11" t="n"/>
       <c r="X249" s="11" t="n"/>
       <c r="Y249" s="11" t="n"/>
+      <c r="Z249" s="11" t="n"/>
+      <c r="AA249" s="11" t="n"/>
+      <c r="AB249" s="11" t="n"/>
+      <c r="AC249" s="11" t="n"/>
+      <c r="AD249" s="11" t="n"/>
+      <c r="AE249" s="11" t="n"/>
+      <c r="AF249" s="11" t="n"/>
+      <c r="AG249" s="11" t="n"/>
+      <c r="AH249" s="11" t="n"/>
+      <c r="AI249" s="11" t="n"/>
+      <c r="AJ249" s="11" t="n"/>
+      <c r="AK249" s="11" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="5" t="n"/>
@@ -8323,6 +11416,18 @@
       <c r="W250" s="11" t="n"/>
       <c r="X250" s="11" t="n"/>
       <c r="Y250" s="11" t="n"/>
+      <c r="Z250" s="11" t="n"/>
+      <c r="AA250" s="11" t="n"/>
+      <c r="AB250" s="11" t="n"/>
+      <c r="AC250" s="11" t="n"/>
+      <c r="AD250" s="11" t="n"/>
+      <c r="AE250" s="11" t="n"/>
+      <c r="AF250" s="11" t="n"/>
+      <c r="AG250" s="11" t="n"/>
+      <c r="AH250" s="11" t="n"/>
+      <c r="AI250" s="11" t="n"/>
+      <c r="AJ250" s="11" t="n"/>
+      <c r="AK250" s="11" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="5" t="n"/>
@@ -8350,6 +11455,18 @@
       <c r="W251" s="11" t="n"/>
       <c r="X251" s="11" t="n"/>
       <c r="Y251" s="11" t="n"/>
+      <c r="Z251" s="11" t="n"/>
+      <c r="AA251" s="11" t="n"/>
+      <c r="AB251" s="11" t="n"/>
+      <c r="AC251" s="11" t="n"/>
+      <c r="AD251" s="11" t="n"/>
+      <c r="AE251" s="11" t="n"/>
+      <c r="AF251" s="11" t="n"/>
+      <c r="AG251" s="11" t="n"/>
+      <c r="AH251" s="11" t="n"/>
+      <c r="AI251" s="11" t="n"/>
+      <c r="AJ251" s="11" t="n"/>
+      <c r="AK251" s="11" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n"/>
@@ -8377,6 +11494,18 @@
       <c r="W252" s="11" t="n"/>
       <c r="X252" s="11" t="n"/>
       <c r="Y252" s="11" t="n"/>
+      <c r="Z252" s="11" t="n"/>
+      <c r="AA252" s="11" t="n"/>
+      <c r="AB252" s="11" t="n"/>
+      <c r="AC252" s="11" t="n"/>
+      <c r="AD252" s="11" t="n"/>
+      <c r="AE252" s="11" t="n"/>
+      <c r="AF252" s="11" t="n"/>
+      <c r="AG252" s="11" t="n"/>
+      <c r="AH252" s="11" t="n"/>
+      <c r="AI252" s="11" t="n"/>
+      <c r="AJ252" s="11" t="n"/>
+      <c r="AK252" s="11" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="n"/>
@@ -8404,6 +11533,18 @@
       <c r="W253" s="11" t="n"/>
       <c r="X253" s="11" t="n"/>
       <c r="Y253" s="11" t="n"/>
+      <c r="Z253" s="11" t="n"/>
+      <c r="AA253" s="11" t="n"/>
+      <c r="AB253" s="11" t="n"/>
+      <c r="AC253" s="11" t="n"/>
+      <c r="AD253" s="11" t="n"/>
+      <c r="AE253" s="11" t="n"/>
+      <c r="AF253" s="11" t="n"/>
+      <c r="AG253" s="11" t="n"/>
+      <c r="AH253" s="11" t="n"/>
+      <c r="AI253" s="11" t="n"/>
+      <c r="AJ253" s="11" t="n"/>
+      <c r="AK253" s="11" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="5" t="n"/>
@@ -8431,6 +11572,18 @@
       <c r="W254" s="11" t="n"/>
       <c r="X254" s="11" t="n"/>
       <c r="Y254" s="11" t="n"/>
+      <c r="Z254" s="11" t="n"/>
+      <c r="AA254" s="11" t="n"/>
+      <c r="AB254" s="11" t="n"/>
+      <c r="AC254" s="11" t="n"/>
+      <c r="AD254" s="11" t="n"/>
+      <c r="AE254" s="11" t="n"/>
+      <c r="AF254" s="11" t="n"/>
+      <c r="AG254" s="11" t="n"/>
+      <c r="AH254" s="11" t="n"/>
+      <c r="AI254" s="11" t="n"/>
+      <c r="AJ254" s="11" t="n"/>
+      <c r="AK254" s="11" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="5" t="n"/>
@@ -8458,6 +11611,18 @@
       <c r="W255" s="11" t="n"/>
       <c r="X255" s="11" t="n"/>
       <c r="Y255" s="11" t="n"/>
+      <c r="Z255" s="11" t="n"/>
+      <c r="AA255" s="11" t="n"/>
+      <c r="AB255" s="11" t="n"/>
+      <c r="AC255" s="11" t="n"/>
+      <c r="AD255" s="11" t="n"/>
+      <c r="AE255" s="11" t="n"/>
+      <c r="AF255" s="11" t="n"/>
+      <c r="AG255" s="11" t="n"/>
+      <c r="AH255" s="11" t="n"/>
+      <c r="AI255" s="11" t="n"/>
+      <c r="AJ255" s="11" t="n"/>
+      <c r="AK255" s="11" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n"/>
@@ -8485,6 +11650,18 @@
       <c r="W256" s="11" t="n"/>
       <c r="X256" s="11" t="n"/>
       <c r="Y256" s="11" t="n"/>
+      <c r="Z256" s="11" t="n"/>
+      <c r="AA256" s="11" t="n"/>
+      <c r="AB256" s="11" t="n"/>
+      <c r="AC256" s="11" t="n"/>
+      <c r="AD256" s="11" t="n"/>
+      <c r="AE256" s="11" t="n"/>
+      <c r="AF256" s="11" t="n"/>
+      <c r="AG256" s="11" t="n"/>
+      <c r="AH256" s="11" t="n"/>
+      <c r="AI256" s="11" t="n"/>
+      <c r="AJ256" s="11" t="n"/>
+      <c r="AK256" s="11" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n"/>
@@ -8512,6 +11689,18 @@
       <c r="W257" s="11" t="n"/>
       <c r="X257" s="11" t="n"/>
       <c r="Y257" s="11" t="n"/>
+      <c r="Z257" s="11" t="n"/>
+      <c r="AA257" s="11" t="n"/>
+      <c r="AB257" s="11" t="n"/>
+      <c r="AC257" s="11" t="n"/>
+      <c r="AD257" s="11" t="n"/>
+      <c r="AE257" s="11" t="n"/>
+      <c r="AF257" s="11" t="n"/>
+      <c r="AG257" s="11" t="n"/>
+      <c r="AH257" s="11" t="n"/>
+      <c r="AI257" s="11" t="n"/>
+      <c r="AJ257" s="11" t="n"/>
+      <c r="AK257" s="11" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="5" t="n"/>
@@ -8539,6 +11728,18 @@
       <c r="W258" s="11" t="n"/>
       <c r="X258" s="11" t="n"/>
       <c r="Y258" s="11" t="n"/>
+      <c r="Z258" s="11" t="n"/>
+      <c r="AA258" s="11" t="n"/>
+      <c r="AB258" s="11" t="n"/>
+      <c r="AC258" s="11" t="n"/>
+      <c r="AD258" s="11" t="n"/>
+      <c r="AE258" s="11" t="n"/>
+      <c r="AF258" s="11" t="n"/>
+      <c r="AG258" s="11" t="n"/>
+      <c r="AH258" s="11" t="n"/>
+      <c r="AI258" s="11" t="n"/>
+      <c r="AJ258" s="11" t="n"/>
+      <c r="AK258" s="11" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="5" t="n"/>
@@ -8566,6 +11767,18 @@
       <c r="W259" s="11" t="n"/>
       <c r="X259" s="11" t="n"/>
       <c r="Y259" s="11" t="n"/>
+      <c r="Z259" s="11" t="n"/>
+      <c r="AA259" s="11" t="n"/>
+      <c r="AB259" s="11" t="n"/>
+      <c r="AC259" s="11" t="n"/>
+      <c r="AD259" s="11" t="n"/>
+      <c r="AE259" s="11" t="n"/>
+      <c r="AF259" s="11" t="n"/>
+      <c r="AG259" s="11" t="n"/>
+      <c r="AH259" s="11" t="n"/>
+      <c r="AI259" s="11" t="n"/>
+      <c r="AJ259" s="11" t="n"/>
+      <c r="AK259" s="11" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n"/>
@@ -8593,6 +11806,18 @@
       <c r="W260" s="11" t="n"/>
       <c r="X260" s="11" t="n"/>
       <c r="Y260" s="11" t="n"/>
+      <c r="Z260" s="11" t="n"/>
+      <c r="AA260" s="11" t="n"/>
+      <c r="AB260" s="11" t="n"/>
+      <c r="AC260" s="11" t="n"/>
+      <c r="AD260" s="11" t="n"/>
+      <c r="AE260" s="11" t="n"/>
+      <c r="AF260" s="11" t="n"/>
+      <c r="AG260" s="11" t="n"/>
+      <c r="AH260" s="11" t="n"/>
+      <c r="AI260" s="11" t="n"/>
+      <c r="AJ260" s="11" t="n"/>
+      <c r="AK260" s="11" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n"/>
@@ -8620,6 +11845,18 @@
       <c r="W261" s="11" t="n"/>
       <c r="X261" s="11" t="n"/>
       <c r="Y261" s="11" t="n"/>
+      <c r="Z261" s="11" t="n"/>
+      <c r="AA261" s="11" t="n"/>
+      <c r="AB261" s="11" t="n"/>
+      <c r="AC261" s="11" t="n"/>
+      <c r="AD261" s="11" t="n"/>
+      <c r="AE261" s="11" t="n"/>
+      <c r="AF261" s="11" t="n"/>
+      <c r="AG261" s="11" t="n"/>
+      <c r="AH261" s="11" t="n"/>
+      <c r="AI261" s="11" t="n"/>
+      <c r="AJ261" s="11" t="n"/>
+      <c r="AK261" s="11" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="5" t="n"/>
@@ -8647,9 +11884,21 @@
       <c r="W262" s="5" t="n"/>
       <c r="X262" s="5" t="n"/>
       <c r="Y262" s="5" t="n"/>
+      <c r="Z262" s="5" t="n"/>
+      <c r="AA262" s="5" t="n"/>
+      <c r="AB262" s="5" t="n"/>
+      <c r="AC262" s="5" t="n"/>
+      <c r="AD262" s="5" t="n"/>
+      <c r="AE262" s="5" t="n"/>
+      <c r="AF262" s="5" t="n"/>
+      <c r="AG262" s="5" t="n"/>
+      <c r="AH262" s="5" t="n"/>
+      <c r="AI262" s="5" t="n"/>
+      <c r="AJ262" s="5" t="n"/>
+      <c r="AK262" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y262"/>
+  <autoFilter ref="A1:AK262"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/portal/templates/01 Xero P&L.xlsx
+++ b/portal/templates/01 Xero P&L.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P&amp;L'!$A$1:$AK$262</definedName>
